--- a/data/SOCIAL ACTIVE TEMPERE SOLIDAIRE.xlsx
+++ b/data/SOCIAL ACTIVE TEMPERE SOLIDAIRE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t>Historique Cours</t>
   </si>
@@ -20,37 +20,55 @@
     <t>Date d'export</t>
   </si>
   <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>Valeur :</t>
+  </si>
+  <si>
+    <t>Libellé valeur :</t>
+  </si>
+  <si>
+    <t>Code Isin :</t>
+  </si>
+  <si>
+    <t>S.A. TEMPERE SOLID</t>
+  </si>
+  <si>
+    <t>000010001620</t>
+  </si>
+  <si>
+    <t>Se rendre en bas du document</t>
+  </si>
+  <si>
+    <t>Date de cotation</t>
+  </si>
+  <si>
+    <t>Dernier cours en EUR</t>
+  </si>
+  <si>
+    <t>Evolution en %</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
     <t>31/10/2025</t>
-  </si>
-  <si>
-    <t>Valeur :</t>
-  </si>
-  <si>
-    <t>Libellé valeur :</t>
-  </si>
-  <si>
-    <t>Code Isin :</t>
-  </si>
-  <si>
-    <t>S.A. TEMPERE SOLID</t>
-  </si>
-  <si>
-    <t>000010001620</t>
-  </si>
-  <si>
-    <t>Se rendre en bas du document</t>
-  </si>
-  <si>
-    <t>Date de cotation</t>
-  </si>
-  <si>
-    <t>Dernier cours en EUR</t>
-  </si>
-  <si>
-    <t>Evolution en %</t>
-  </si>
-  <si>
-    <t>Volume</t>
   </si>
   <si>
     <t>30/09/2025</t>
@@ -1093,8 +1111,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D267" headerRowCount="1">
-  <autoFilter ref="A7:D267"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D273" headerRowCount="1">
+  <autoFilter ref="A7:D273"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Date de cotation"/>
     <tableColumn id="2" name="Dernier cours en EUR"/>
@@ -1107,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1" style="1"/>
@@ -1221,13 +1239,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="14">
-        <v>15.7809</v>
+        <v>15.4606</v>
       </c>
       <c r="C8" s="15">
-        <v>0.09</v>
+        <v>-4.14</v>
       </c>
       <c r="D8" s="16">
-        <v>27958865</v>
+        <v>25607229</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1237,13 +1255,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="14">
-        <v>15.7666</v>
+        <v>16.1277</v>
       </c>
       <c r="C9" s="15">
-        <v>-0.26</v>
+        <v>1.38</v>
       </c>
       <c r="D9" s="16">
-        <v>28144179</v>
+        <v>26983224</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1253,13 +1271,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="14">
-        <v>15.8083</v>
+        <v>15.9084</v>
       </c>
       <c r="C10" s="15">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="D10" s="16">
-        <v>28208442</v>
+        <v>27209514</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1269,13 +1287,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="14">
-        <v>15.7176</v>
+        <v>15.8442</v>
       </c>
       <c r="C11" s="15">
-        <v>-0.3</v>
+        <v>0.02</v>
       </c>
       <c r="D11" s="16">
-        <v>28147007</v>
+        <v>27486255</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1285,13 +1303,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="14">
-        <v>15.7645</v>
+        <v>15.8411</v>
       </c>
       <c r="C12" s="15">
-        <v>1.25</v>
+        <v>-0.15</v>
       </c>
       <c r="D12" s="16">
-        <v>27529765</v>
+        <v>27540208</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1301,13 +1319,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="14">
-        <v>15.5705</v>
+        <v>15.8651</v>
       </c>
       <c r="C13" s="15">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="D13" s="16">
-        <v>26537148</v>
+        <v>27732431</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1317,13 +1335,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="14">
-        <v>15.454</v>
+        <v>15.7809</v>
       </c>
       <c r="C14" s="15">
-        <v>-1.46</v>
+        <v>0.09</v>
       </c>
       <c r="D14" s="16">
-        <v>26410715</v>
+        <v>27958865</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1333,13 +1351,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="14">
-        <v>15.6831</v>
+        <v>15.7666</v>
       </c>
       <c r="C15" s="15">
-        <v>1.11</v>
+        <v>-0.26</v>
       </c>
       <c r="D15" s="16">
-        <v>26632265</v>
+        <v>28144179</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1349,13 +1367,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="14">
-        <v>15.5112</v>
+        <v>15.8083</v>
       </c>
       <c r="C16" s="15">
-        <v>1.67</v>
+        <v>0.58</v>
       </c>
       <c r="D16" s="16">
-        <v>26690099</v>
+        <v>28208442</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1365,13 +1383,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="14">
-        <v>15.2564</v>
+        <v>15.7176</v>
       </c>
       <c r="C17" s="15">
-        <v>0.09</v>
+        <v>-0.3</v>
       </c>
       <c r="D17" s="16">
-        <v>26845237</v>
+        <v>28147007</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1381,13 +1399,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="14">
-        <v>15.2426</v>
+        <v>15.7645</v>
       </c>
       <c r="C18" s="15">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="D18" s="16">
-        <v>26818264</v>
+        <v>27529765</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1397,13 +1415,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="14">
-        <v>15.135</v>
+        <v>15.5705</v>
       </c>
       <c r="C19" s="15">
-        <v>-1.04</v>
+        <v>0.75</v>
       </c>
       <c r="D19" s="16">
-        <v>26929428</v>
+        <v>26537148</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1413,13 +1431,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="14">
-        <v>15.2933</v>
+        <v>15.454</v>
       </c>
       <c r="C20" s="15">
-        <v>0.89</v>
+        <v>-1.46</v>
       </c>
       <c r="D20" s="16">
-        <v>27020006</v>
+        <v>26410715</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1429,13 +1447,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="14">
-        <v>15.1584</v>
+        <v>15.6831</v>
       </c>
       <c r="C21" s="15">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="D21" s="16">
-        <v>27124319</v>
+        <v>26632265</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1445,13 +1463,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="14">
-        <v>15.0816</v>
+        <v>15.5112</v>
       </c>
       <c r="C22" s="15">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="D22" s="16">
-        <v>27294390</v>
+        <v>26690099</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1461,13 +1479,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="14">
-        <v>14.9271</v>
+        <v>15.2564</v>
       </c>
       <c r="C23" s="15">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="D23" s="16">
-        <v>27314404</v>
+        <v>26845237</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1477,13 +1495,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="14">
-        <v>14.9928</v>
+        <v>15.2426</v>
       </c>
       <c r="C24" s="15">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="D24" s="16">
-        <v>26939895</v>
+        <v>26818264</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1493,13 +1511,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="14">
-        <v>14.8465</v>
+        <v>15.135</v>
       </c>
       <c r="C25" s="15">
-        <v>-0.68</v>
+        <v>-1.04</v>
       </c>
       <c r="D25" s="16">
-        <v>25973217</v>
+        <v>26929428</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1509,13 +1527,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="14">
-        <v>14.9485</v>
+        <v>15.2933</v>
       </c>
       <c r="C26" s="15">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="D26" s="16">
-        <v>25671577</v>
+        <v>27020006</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -1525,13 +1543,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="14">
-        <v>14.7835</v>
+        <v>15.1584</v>
       </c>
       <c r="C27" s="15">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="D27" s="16">
-        <v>25820021</v>
+        <v>27124319</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -1541,13 +1559,13 @@
         <v>33</v>
       </c>
       <c r="B28" s="14">
-        <v>14.7222</v>
+        <v>15.0816</v>
       </c>
       <c r="C28" s="15">
-        <v>-0.1</v>
+        <v>1.04</v>
       </c>
       <c r="D28" s="16">
-        <v>26385972</v>
+        <v>27294390</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -1557,13 +1575,13 @@
         <v>34</v>
       </c>
       <c r="B29" s="14">
-        <v>14.7365</v>
+        <v>14.9271</v>
       </c>
       <c r="C29" s="15">
-        <v>2.34</v>
+        <v>-0.44</v>
       </c>
       <c r="D29" s="16">
-        <v>26664397</v>
+        <v>27314404</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1573,13 +1591,13 @@
         <v>35</v>
       </c>
       <c r="B30" s="14">
-        <v>14.4003</v>
+        <v>14.9928</v>
       </c>
       <c r="C30" s="15">
-        <v>3.26</v>
+        <v>0.99</v>
       </c>
       <c r="D30" s="16">
-        <v>26756224</v>
+        <v>26939895</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1589,13 +1607,13 @@
         <v>36</v>
       </c>
       <c r="B31" s="14">
-        <v>13.9463</v>
+        <v>14.8465</v>
       </c>
       <c r="C31" s="15">
-        <v>-0.49</v>
+        <v>-0.68</v>
       </c>
       <c r="D31" s="16">
-        <v>27100615</v>
+        <v>25973217</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -1605,13 +1623,13 @@
         <v>37</v>
       </c>
       <c r="B32" s="14">
-        <v>14.0155</v>
+        <v>14.9485</v>
       </c>
       <c r="C32" s="15">
-        <v>-1.18</v>
+        <v>1.12</v>
       </c>
       <c r="D32" s="16">
-        <v>27434822</v>
+        <v>25671577</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
@@ -1621,13 +1639,13 @@
         <v>38</v>
       </c>
       <c r="B33" s="14">
-        <v>14.1832</v>
+        <v>14.7835</v>
       </c>
       <c r="C33" s="15">
-        <v>-0.74</v>
+        <v>0.42</v>
       </c>
       <c r="D33" s="16">
-        <v>27612041</v>
+        <v>25820021</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1637,13 +1655,13 @@
         <v>39</v>
       </c>
       <c r="B34" s="14">
-        <v>14.2882</v>
+        <v>14.7222</v>
       </c>
       <c r="C34" s="15">
-        <v>1.03</v>
+        <v>-0.1</v>
       </c>
       <c r="D34" s="16">
-        <v>27609778</v>
+        <v>26385972</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1653,13 +1671,13 @@
         <v>40</v>
       </c>
       <c r="B35" s="14">
-        <v>14.1431</v>
+        <v>14.7365</v>
       </c>
       <c r="C35" s="15">
-        <v>0.44</v>
+        <v>2.34</v>
       </c>
       <c r="D35" s="16">
-        <v>27618876</v>
+        <v>26664397</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -1669,13 +1687,13 @@
         <v>41</v>
       </c>
       <c r="B36" s="14">
-        <v>14.0815</v>
+        <v>14.4003</v>
       </c>
       <c r="C36" s="15">
-        <v>-0.43</v>
+        <v>3.26</v>
       </c>
       <c r="D36" s="16">
-        <v>27173910</v>
+        <v>26756224</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1685,13 +1703,13 @@
         <v>42</v>
       </c>
       <c r="B37" s="14">
-        <v>14.1424</v>
+        <v>13.9463</v>
       </c>
       <c r="C37" s="15">
-        <v>0.89</v>
+        <v>-0.49</v>
       </c>
       <c r="D37" s="16">
-        <v>26373626</v>
+        <v>27100615</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -1701,13 +1719,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="14">
-        <v>14.0179</v>
+        <v>14.0155</v>
       </c>
       <c r="C38" s="15">
-        <v>1.09</v>
+        <v>-1.18</v>
       </c>
       <c r="D38" s="16">
-        <v>26516596</v>
+        <v>27434822</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -1717,13 +1735,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="14">
-        <v>13.8662</v>
+        <v>14.1832</v>
       </c>
       <c r="C39" s="15">
-        <v>-0.46</v>
+        <v>-0.74</v>
       </c>
       <c r="D39" s="16">
-        <v>26953299</v>
+        <v>27612041</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -1733,13 +1751,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="14">
-        <v>13.9307</v>
+        <v>14.2882</v>
       </c>
       <c r="C40" s="15">
-        <v>2.95</v>
+        <v>1.03</v>
       </c>
       <c r="D40" s="16">
-        <v>27138500</v>
+        <v>27609778</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -1749,13 +1767,13 @@
         <v>46</v>
       </c>
       <c r="B41" s="14">
-        <v>13.532</v>
+        <v>14.1431</v>
       </c>
       <c r="C41" s="15">
-        <v>-1.87</v>
+        <v>0.44</v>
       </c>
       <c r="D41" s="16">
-        <v>27375019</v>
+        <v>27618876</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -1765,13 +1783,13 @@
         <v>47</v>
       </c>
       <c r="B42" s="14">
-        <v>13.7904</v>
+        <v>14.0815</v>
       </c>
       <c r="C42" s="15">
-        <v>2.68</v>
+        <v>-0.43</v>
       </c>
       <c r="D42" s="16">
-        <v>27611383</v>
+        <v>27173910</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1781,13 +1799,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="14">
-        <v>13.4301</v>
+        <v>14.1424</v>
       </c>
       <c r="C43" s="15">
-        <v>1.4</v>
+        <v>0.89</v>
       </c>
       <c r="D43" s="16">
-        <v>27712668</v>
+        <v>26373626</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -1797,13 +1815,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="14">
-        <v>13.2445</v>
+        <v>14.0179</v>
       </c>
       <c r="C44" s="15">
-        <v>-2.9</v>
+        <v>1.09</v>
       </c>
       <c r="D44" s="16">
-        <v>28141058</v>
+        <v>26516596</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -1813,13 +1831,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="14">
-        <v>13.6393</v>
+        <v>13.8662</v>
       </c>
       <c r="C45" s="15">
-        <v>-3.67</v>
+        <v>-0.46</v>
       </c>
       <c r="D45" s="16">
-        <v>28579838</v>
+        <v>26953299</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -1829,13 +1847,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="14">
-        <v>14.1582</v>
+        <v>13.9307</v>
       </c>
       <c r="C46" s="15">
-        <v>3.68</v>
+        <v>2.95</v>
       </c>
       <c r="D46" s="16">
-        <v>28682522</v>
+        <v>27138500</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -1845,13 +1863,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="14">
-        <v>13.6559</v>
+        <v>13.532</v>
       </c>
       <c r="C47" s="15">
-        <v>-3.26</v>
+        <v>-1.87</v>
       </c>
       <c r="D47" s="16">
-        <v>28723130</v>
+        <v>27375019</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -1861,13 +1879,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="14">
-        <v>14.1159</v>
+        <v>13.7904</v>
       </c>
       <c r="C48" s="15">
-        <v>-0.84</v>
+        <v>2.68</v>
       </c>
       <c r="D48" s="16">
-        <v>28480323</v>
+        <v>27611383</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -1877,13 +1895,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="14">
-        <v>14.2348</v>
+        <v>13.4301</v>
       </c>
       <c r="C49" s="15">
-        <v>-1.95</v>
+        <v>1.4</v>
       </c>
       <c r="D49" s="16">
-        <v>27391640</v>
+        <v>27712668</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -1893,13 +1911,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="14">
-        <v>14.5183</v>
+        <v>13.2445</v>
       </c>
       <c r="C50" s="15">
-        <v>-1.06</v>
+        <v>-2.9</v>
       </c>
       <c r="D50" s="16">
-        <v>27176414</v>
+        <v>28141058</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -1909,13 +1927,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="14">
-        <v>14.6738</v>
+        <v>13.6393</v>
       </c>
       <c r="C51" s="15">
-        <v>-2.4</v>
+        <v>-3.67</v>
       </c>
       <c r="D51" s="16">
-        <v>27648035</v>
+        <v>28579838</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -1925,13 +1943,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="14">
-        <v>15.0341</v>
+        <v>14.1582</v>
       </c>
       <c r="C52" s="15">
-        <v>-2.18</v>
+        <v>3.68</v>
       </c>
       <c r="D52" s="16">
-        <v>27793878</v>
+        <v>28682522</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -1941,13 +1959,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="14">
-        <v>15.3697</v>
+        <v>13.6559</v>
       </c>
       <c r="C53" s="15">
-        <v>1.06</v>
+        <v>-3.26</v>
       </c>
       <c r="D53" s="16">
-        <v>27629335</v>
+        <v>28723130</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1957,13 +1975,13 @@
         <v>59</v>
       </c>
       <c r="B54" s="14">
-        <v>15.2091</v>
+        <v>14.1159</v>
       </c>
       <c r="C54" s="15">
-        <v>-0.29</v>
+        <v>-0.84</v>
       </c>
       <c r="D54" s="16">
-        <v>27204612</v>
+        <v>28480323</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -1973,13 +1991,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="14">
-        <v>15.2538</v>
+        <v>14.2348</v>
       </c>
       <c r="C55" s="15">
-        <v>0.73</v>
+        <v>-1.95</v>
       </c>
       <c r="D55" s="16">
-        <v>27113066</v>
+        <v>27391640</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -1989,13 +2007,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="14">
-        <v>15.144</v>
+        <v>14.5183</v>
       </c>
       <c r="C56" s="15">
-        <v>-1.28</v>
+        <v>-1.06</v>
       </c>
       <c r="D56" s="16">
-        <v>27182928</v>
+        <v>27176414</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -2005,13 +2023,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="14">
-        <v>15.3402</v>
+        <v>14.6738</v>
       </c>
       <c r="C57" s="15">
-        <v>0.52</v>
+        <v>-2.4</v>
       </c>
       <c r="D57" s="16">
-        <v>27428081</v>
+        <v>27648035</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -2021,13 +2039,13 @@
         <v>63</v>
       </c>
       <c r="B58" s="14">
-        <v>15.2612</v>
+        <v>15.0341</v>
       </c>
       <c r="C58" s="15">
-        <v>0.79</v>
+        <v>-2.18</v>
       </c>
       <c r="D58" s="16">
-        <v>27409830</v>
+        <v>27793878</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -2037,13 +2055,13 @@
         <v>64</v>
       </c>
       <c r="B59" s="14">
-        <v>15.1419</v>
+        <v>15.3697</v>
       </c>
       <c r="C59" s="15">
-        <v>0.41</v>
+        <v>1.06</v>
       </c>
       <c r="D59" s="16">
-        <v>27240164</v>
+        <v>27629335</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -2053,13 +2071,13 @@
         <v>65</v>
       </c>
       <c r="B60" s="14">
-        <v>15.0805</v>
+        <v>15.2091</v>
       </c>
       <c r="C60" s="15">
-        <v>0.49</v>
+        <v>-0.29</v>
       </c>
       <c r="D60" s="16">
-        <v>26175558</v>
+        <v>27204612</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -2069,13 +2087,13 @@
         <v>66</v>
       </c>
       <c r="B61" s="14">
-        <v>15.0077</v>
+        <v>15.2538</v>
       </c>
       <c r="C61" s="15">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="D61" s="16">
-        <v>24579635</v>
+        <v>27113066</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -2085,13 +2103,13 @@
         <v>67</v>
       </c>
       <c r="B62" s="14">
-        <v>14.9567</v>
+        <v>15.144</v>
       </c>
       <c r="C62" s="15">
-        <v>1.57</v>
+        <v>-1.28</v>
       </c>
       <c r="D62" s="16">
-        <v>23850708</v>
+        <v>27182928</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -2101,13 +2119,13 @@
         <v>68</v>
       </c>
       <c r="B63" s="14">
-        <v>14.7259</v>
+        <v>15.3402</v>
       </c>
       <c r="C63" s="15">
-        <v>0.18</v>
+        <v>0.52</v>
       </c>
       <c r="D63" s="16">
-        <v>23635941</v>
+        <v>27428081</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -2117,13 +2135,13 @@
         <v>69</v>
       </c>
       <c r="B64" s="14">
-        <v>14.6994</v>
+        <v>15.2612</v>
       </c>
       <c r="C64" s="15">
-        <v>-0.47</v>
+        <v>0.79</v>
       </c>
       <c r="D64" s="16">
-        <v>23438140</v>
+        <v>27409830</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -2133,13 +2151,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="14">
-        <v>14.7691</v>
+        <v>15.1419</v>
       </c>
       <c r="C65" s="15">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="D65" s="16">
-        <v>23337460</v>
+        <v>27240164</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -2149,13 +2167,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="14">
-        <v>14.7203</v>
+        <v>15.0805</v>
       </c>
       <c r="C66" s="15">
-        <v>3.01</v>
+        <v>0.49</v>
       </c>
       <c r="D66" s="16">
-        <v>22878949</v>
+        <v>26175558</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -2165,13 +2183,13 @@
         <v>72</v>
       </c>
       <c r="B67" s="14">
-        <v>14.2904</v>
+        <v>15.0077</v>
       </c>
       <c r="C67" s="15">
-        <v>-1.11</v>
+        <v>0.34</v>
       </c>
       <c r="D67" s="16">
-        <v>22682017</v>
+        <v>24579635</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -2181,13 +2199,13 @@
         <v>73</v>
       </c>
       <c r="B68" s="14">
-        <v>14.4513</v>
+        <v>14.9567</v>
       </c>
       <c r="C68" s="15">
-        <v>-0.24</v>
+        <v>1.57</v>
       </c>
       <c r="D68" s="16">
-        <v>22456814</v>
+        <v>23850708</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -2197,13 +2215,13 @@
         <v>74</v>
       </c>
       <c r="B69" s="14">
-        <v>14.4862</v>
+        <v>14.7259</v>
       </c>
       <c r="C69" s="15">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="D69" s="16">
-        <v>22273337</v>
+        <v>23635941</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -2213,13 +2231,13 @@
         <v>75</v>
       </c>
       <c r="B70" s="14">
-        <v>14.4221</v>
+        <v>14.6994</v>
       </c>
       <c r="C70" s="15">
-        <v>0.08</v>
+        <v>-0.47</v>
       </c>
       <c r="D70" s="16">
-        <v>22059075</v>
+        <v>23438140</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -2229,13 +2247,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="14">
-        <v>14.41</v>
+        <v>14.7691</v>
       </c>
       <c r="C71" s="15">
-        <v>1.55</v>
+        <v>0.33</v>
       </c>
       <c r="D71" s="16">
-        <v>21534754</v>
+        <v>23337460</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -2245,13 +2263,13 @@
         <v>77</v>
       </c>
       <c r="B72" s="14">
-        <v>14.1899</v>
+        <v>14.7203</v>
       </c>
       <c r="C72" s="15">
-        <v>0.96</v>
+        <v>3.01</v>
       </c>
       <c r="D72" s="16">
-        <v>20601299</v>
+        <v>22878949</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -2261,13 +2279,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="14">
-        <v>14.0544</v>
+        <v>14.2904</v>
       </c>
       <c r="C73" s="15">
-        <v>1.71</v>
+        <v>-1.11</v>
       </c>
       <c r="D73" s="16">
-        <v>20180084</v>
+        <v>22682017</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
@@ -2277,13 +2295,13 @@
         <v>79</v>
       </c>
       <c r="B74" s="14">
-        <v>13.8179</v>
+        <v>14.4513</v>
       </c>
       <c r="C74" s="15">
-        <v>-2.09</v>
+        <v>-0.24</v>
       </c>
       <c r="D74" s="16">
-        <v>20063482</v>
+        <v>22456814</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
@@ -2293,13 +2311,13 @@
         <v>80</v>
       </c>
       <c r="B75" s="14">
-        <v>14.1131</v>
+        <v>14.4862</v>
       </c>
       <c r="C75" s="15">
-        <v>-1.24</v>
+        <v>0.44</v>
       </c>
       <c r="D75" s="16">
-        <v>20604649</v>
+        <v>22273337</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
@@ -2309,13 +2327,13 @@
         <v>81</v>
       </c>
       <c r="B76" s="14">
-        <v>14.2903</v>
+        <v>14.4221</v>
       </c>
       <c r="C76" s="15">
-        <v>-0.16</v>
+        <v>0.08</v>
       </c>
       <c r="D76" s="16">
-        <v>20591533</v>
+        <v>22059075</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
@@ -2325,13 +2343,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="14">
-        <v>14.3138</v>
+        <v>14.41</v>
       </c>
       <c r="C77" s="15">
-        <v>-0.03</v>
+        <v>1.55</v>
       </c>
       <c r="D77" s="16">
-        <v>20416510</v>
+        <v>21534754</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
@@ -2341,13 +2359,13 @@
         <v>83</v>
       </c>
       <c r="B78" s="14">
-        <v>14.3184</v>
+        <v>14.1899</v>
       </c>
       <c r="C78" s="15">
-        <v>0.34</v>
+        <v>0.96</v>
       </c>
       <c r="D78" s="16">
-        <v>20375465</v>
+        <v>20601299</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -2357,13 +2375,13 @@
         <v>84</v>
       </c>
       <c r="B79" s="14">
-        <v>14.2694</v>
+        <v>14.0544</v>
       </c>
       <c r="C79" s="15">
-        <v>0.02</v>
+        <v>1.71</v>
       </c>
       <c r="D79" s="16">
-        <v>20292025</v>
+        <v>20180084</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
@@ -2373,13 +2391,13 @@
         <v>85</v>
       </c>
       <c r="B80" s="14">
-        <v>14.266</v>
+        <v>13.8179</v>
       </c>
       <c r="C80" s="15">
-        <v>0.23</v>
+        <v>-2.09</v>
       </c>
       <c r="D80" s="16">
-        <v>20329763</v>
+        <v>20063482</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
@@ -2389,13 +2407,13 @@
         <v>86</v>
       </c>
       <c r="B81" s="14">
-        <v>14.2337</v>
+        <v>14.1131</v>
       </c>
       <c r="C81" s="15">
-        <v>-0.17</v>
+        <v>-1.24</v>
       </c>
       <c r="D81" s="16">
-        <v>20319771</v>
+        <v>20604649</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2405,13 +2423,13 @@
         <v>87</v>
       </c>
       <c r="B82" s="14">
-        <v>14.2572</v>
+        <v>14.2903</v>
       </c>
       <c r="C82" s="15">
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="D82" s="16">
-        <v>20372415</v>
+        <v>20591533</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
@@ -2421,13 +2439,13 @@
         <v>88</v>
       </c>
       <c r="B83" s="14">
-        <v>14.2319</v>
+        <v>14.3138</v>
       </c>
       <c r="C83" s="15">
-        <v>1.18</v>
+        <v>-0.03</v>
       </c>
       <c r="D83" s="16">
-        <v>20322696</v>
+        <v>20416510</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
@@ -2437,13 +2455,13 @@
         <v>89</v>
       </c>
       <c r="B84" s="14">
-        <v>14.0663</v>
+        <v>14.3184</v>
       </c>
       <c r="C84" s="15">
-        <v>-0.54</v>
+        <v>0.34</v>
       </c>
       <c r="D84" s="16">
-        <v>19749412</v>
+        <v>20375465</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
@@ -2453,13 +2471,13 @@
         <v>90</v>
       </c>
       <c r="B85" s="14">
-        <v>14.1427</v>
+        <v>14.2694</v>
       </c>
       <c r="C85" s="15">
-        <v>0.86</v>
+        <v>0.02</v>
       </c>
       <c r="D85" s="16">
-        <v>18764505</v>
+        <v>20292025</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
@@ -2469,13 +2487,13 @@
         <v>91</v>
       </c>
       <c r="B86" s="14">
-        <v>14.022</v>
+        <v>14.266</v>
       </c>
       <c r="C86" s="15">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="D86" s="16">
-        <v>18271214</v>
+        <v>20329763</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
@@ -2485,13 +2503,13 @@
         <v>92</v>
       </c>
       <c r="B87" s="14">
-        <v>13.9466</v>
+        <v>14.2337</v>
       </c>
       <c r="C87" s="15">
-        <v>0.65</v>
+        <v>-0.17</v>
       </c>
       <c r="D87" s="16">
-        <v>18210255</v>
+        <v>20319771</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2501,13 +2519,13 @@
         <v>93</v>
       </c>
       <c r="B88" s="14">
-        <v>13.8567</v>
+        <v>14.2572</v>
       </c>
       <c r="C88" s="15">
-        <v>0.8</v>
+        <v>0.18</v>
       </c>
       <c r="D88" s="16">
-        <v>18236514</v>
+        <v>20372415</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
@@ -2517,13 +2535,13 @@
         <v>94</v>
       </c>
       <c r="B89" s="14">
-        <v>13.7473</v>
+        <v>14.2319</v>
       </c>
       <c r="C89" s="15">
-        <v>-0.59</v>
+        <v>1.18</v>
       </c>
       <c r="D89" s="16">
-        <v>18303967</v>
+        <v>20322696</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -2533,13 +2551,13 @@
         <v>95</v>
       </c>
       <c r="B90" s="14">
-        <v>13.8294</v>
+        <v>14.0663</v>
       </c>
       <c r="C90" s="15">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="D90" s="16">
-        <v>18441258</v>
+        <v>19749412</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -2549,13 +2567,13 @@
         <v>96</v>
       </c>
       <c r="B91" s="14">
-        <v>13.8377</v>
+        <v>14.1427</v>
       </c>
       <c r="C91" s="15">
-        <v>-1</v>
+        <v>0.86</v>
       </c>
       <c r="D91" s="16">
-        <v>18545907</v>
+        <v>18764505</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -2565,13 +2583,13 @@
         <v>97</v>
       </c>
       <c r="B92" s="14">
-        <v>13.9769</v>
+        <v>14.022</v>
       </c>
       <c r="C92" s="15">
-        <v>0.07</v>
+        <v>0.54</v>
       </c>
       <c r="D92" s="16">
-        <v>18671095</v>
+        <v>18271214</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -2581,13 +2599,13 @@
         <v>98</v>
       </c>
       <c r="B93" s="14">
-        <v>13.9674</v>
+        <v>13.9466</v>
       </c>
       <c r="C93" s="15">
-        <v>-0.54</v>
+        <v>0.65</v>
       </c>
       <c r="D93" s="16">
-        <v>18776963</v>
+        <v>18210255</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -2597,13 +2615,13 @@
         <v>99</v>
       </c>
       <c r="B94" s="14">
-        <v>14.0435</v>
+        <v>13.8567</v>
       </c>
       <c r="C94" s="15">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="D94" s="16">
-        <v>18835597</v>
+        <v>18236514</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
@@ -2613,13 +2631,13 @@
         <v>100</v>
       </c>
       <c r="B95" s="14">
-        <v>13.9962</v>
+        <v>13.7473</v>
       </c>
       <c r="C95" s="15">
-        <v>0.03</v>
+        <v>-0.59</v>
       </c>
       <c r="D95" s="16">
-        <v>18875257</v>
+        <v>18303967</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
@@ -2629,13 +2647,13 @@
         <v>101</v>
       </c>
       <c r="B96" s="14">
-        <v>13.9922</v>
+        <v>13.8294</v>
       </c>
       <c r="C96" s="15">
-        <v>-0.66</v>
+        <v>-0.06</v>
       </c>
       <c r="D96" s="16">
-        <v>18825827</v>
+        <v>18441258</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
@@ -2645,13 +2663,13 @@
         <v>102</v>
       </c>
       <c r="B97" s="14">
-        <v>14.0845</v>
+        <v>13.8377</v>
       </c>
       <c r="C97" s="15">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
       <c r="D97" s="16">
-        <v>18364121</v>
+        <v>18545907</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -2661,13 +2679,13 @@
         <v>103</v>
       </c>
       <c r="B98" s="14">
-        <v>13.9586</v>
+        <v>13.9769</v>
       </c>
       <c r="C98" s="15">
-        <v>-0.15</v>
+        <v>0.07</v>
       </c>
       <c r="D98" s="16">
-        <v>18284776</v>
+        <v>18671095</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -2677,13 +2695,13 @@
         <v>104</v>
       </c>
       <c r="B99" s="14">
-        <v>13.9788</v>
+        <v>13.9674</v>
       </c>
       <c r="C99" s="15">
-        <v>-0.76</v>
+        <v>-0.54</v>
       </c>
       <c r="D99" s="16">
-        <v>18342371</v>
+        <v>18776963</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -2693,13 +2711,13 @@
         <v>105</v>
       </c>
       <c r="B100" s="14">
-        <v>14.0863</v>
+        <v>14.0435</v>
       </c>
       <c r="C100" s="15">
-        <v>0.07</v>
+        <v>0.34</v>
       </c>
       <c r="D100" s="16">
-        <v>18424532</v>
+        <v>18835597</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -2709,13 +2727,13 @@
         <v>106</v>
       </c>
       <c r="B101" s="14">
-        <v>14.0764</v>
+        <v>13.9962</v>
       </c>
       <c r="C101" s="15">
-        <v>-0.33</v>
+        <v>0.03</v>
       </c>
       <c r="D101" s="16">
-        <v>18445080</v>
+        <v>18875257</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
@@ -2725,13 +2743,13 @@
         <v>107</v>
       </c>
       <c r="B102" s="14">
-        <v>14.1224</v>
+        <v>13.9922</v>
       </c>
       <c r="C102" s="15">
-        <v>-0.42</v>
+        <v>-0.66</v>
       </c>
       <c r="D102" s="16">
-        <v>17813846</v>
+        <v>18825827</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
@@ -2741,13 +2759,13 @@
         <v>108</v>
       </c>
       <c r="B103" s="14">
-        <v>14.1822</v>
+        <v>14.0845</v>
       </c>
       <c r="C103" s="15">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="D103" s="16">
-        <v>17855054</v>
+        <v>18364121</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -2757,13 +2775,13 @@
         <v>109</v>
       </c>
       <c r="B104" s="14">
-        <v>14.095</v>
+        <v>13.9586</v>
       </c>
       <c r="C104" s="15">
-        <v>0.61</v>
+        <v>-0.15</v>
       </c>
       <c r="D104" s="16">
-        <v>17944906</v>
+        <v>18284776</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
@@ -2773,13 +2791,13 @@
         <v>110</v>
       </c>
       <c r="B105" s="14">
-        <v>14.0101</v>
+        <v>13.9788</v>
       </c>
       <c r="C105" s="15">
-        <v>0.1</v>
+        <v>-0.76</v>
       </c>
       <c r="D105" s="16">
-        <v>18048746</v>
+        <v>18342371</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -2789,13 +2807,13 @@
         <v>111</v>
       </c>
       <c r="B106" s="14">
-        <v>13.9959</v>
+        <v>14.0863</v>
       </c>
       <c r="C106" s="15">
-        <v>-0.01</v>
+        <v>0.07</v>
       </c>
       <c r="D106" s="16">
-        <v>18112954</v>
+        <v>18424532</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
@@ -2805,13 +2823,13 @@
         <v>112</v>
       </c>
       <c r="B107" s="14">
-        <v>13.997</v>
+        <v>14.0764</v>
       </c>
       <c r="C107" s="15">
-        <v>-0.63</v>
+        <v>-0.33</v>
       </c>
       <c r="D107" s="16">
-        <v>18156436</v>
+        <v>18445080</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
@@ -2821,13 +2839,13 @@
         <v>113</v>
       </c>
       <c r="B108" s="14">
-        <v>14.0851</v>
+        <v>14.1224</v>
       </c>
       <c r="C108" s="15">
-        <v>0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="D108" s="16">
-        <v>17758697</v>
+        <v>17813846</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
@@ -2837,13 +2855,13 @@
         <v>114</v>
       </c>
       <c r="B109" s="14">
-        <v>14.0615</v>
+        <v>14.1822</v>
       </c>
       <c r="C109" s="15">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="D109" s="16">
-        <v>17190410</v>
+        <v>17855054</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
@@ -2853,13 +2871,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="14">
-        <v>13.9985</v>
+        <v>14.095</v>
       </c>
       <c r="C110" s="15">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="D110" s="16">
-        <v>16952800</v>
+        <v>17944906</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
@@ -2869,13 +2887,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="14">
-        <v>13.9472</v>
+        <v>14.0101</v>
       </c>
       <c r="C111" s="15">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="D111" s="16">
-        <v>16984701</v>
+        <v>18048746</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
@@ -2885,13 +2903,13 @@
         <v>117</v>
       </c>
       <c r="B112" s="14">
-        <v>13.8937</v>
+        <v>13.9959</v>
       </c>
       <c r="C112" s="15">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="D112" s="16">
-        <v>17011954</v>
+        <v>18112954</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
@@ -2901,13 +2919,13 @@
         <v>118</v>
       </c>
       <c r="B113" s="14">
-        <v>13.9847</v>
+        <v>13.997</v>
       </c>
       <c r="C113" s="15">
-        <v>0.95</v>
+        <v>-0.63</v>
       </c>
       <c r="D113" s="16">
-        <v>17035674</v>
+        <v>18156436</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
@@ -2917,13 +2935,13 @@
         <v>119</v>
       </c>
       <c r="B114" s="14">
-        <v>13.8534</v>
+        <v>14.0851</v>
       </c>
       <c r="C114" s="15">
-        <v>-0.34</v>
+        <v>0.17</v>
       </c>
       <c r="D114" s="16">
-        <v>16555499</v>
+        <v>17758697</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
@@ -2933,13 +2951,13 @@
         <v>120</v>
       </c>
       <c r="B115" s="14">
-        <v>13.8999</v>
+        <v>14.0615</v>
       </c>
       <c r="C115" s="15">
-        <v>-0.27</v>
+        <v>0.45</v>
       </c>
       <c r="D115" s="16">
-        <v>16564445</v>
+        <v>17190410</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -2949,13 +2967,13 @@
         <v>121</v>
       </c>
       <c r="B116" s="14">
-        <v>13.9379</v>
+        <v>13.9985</v>
       </c>
       <c r="C116" s="15">
-        <v>0.07</v>
+        <v>0.37</v>
       </c>
       <c r="D116" s="16">
-        <v>16601729</v>
+        <v>16952800</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
@@ -2965,13 +2983,13 @@
         <v>122</v>
       </c>
       <c r="B117" s="14">
-        <v>13.9288</v>
+        <v>13.9472</v>
       </c>
       <c r="C117" s="15">
-        <v>-0.02</v>
+        <v>0.39</v>
       </c>
       <c r="D117" s="16">
-        <v>16602821</v>
+        <v>16984701</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
@@ -2981,13 +2999,13 @@
         <v>123</v>
       </c>
       <c r="B118" s="14">
-        <v>13.9309</v>
+        <v>13.8937</v>
       </c>
       <c r="C118" s="15">
-        <v>0.38</v>
+        <v>-0.65</v>
       </c>
       <c r="D118" s="16">
-        <v>16604572</v>
+        <v>17011954</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
@@ -2997,13 +3015,13 @@
         <v>124</v>
       </c>
       <c r="B119" s="14">
-        <v>13.8785</v>
+        <v>13.9847</v>
       </c>
       <c r="C119" s="15">
-        <v>-0.14</v>
+        <v>0.95</v>
       </c>
       <c r="D119" s="16">
-        <v>16580643</v>
+        <v>17035674</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
@@ -3013,13 +3031,13 @@
         <v>125</v>
       </c>
       <c r="B120" s="14">
-        <v>13.8972</v>
+        <v>13.8534</v>
       </c>
       <c r="C120" s="15">
-        <v>0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="D120" s="16">
-        <v>16067893</v>
+        <v>16555499</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
@@ -3029,13 +3047,13 @@
         <v>126</v>
       </c>
       <c r="B121" s="14">
-        <v>13.8471</v>
+        <v>13.8999</v>
       </c>
       <c r="C121" s="15">
-        <v>0.11</v>
+        <v>-0.27</v>
       </c>
       <c r="D121" s="16">
-        <v>15348175</v>
+        <v>16564445</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
@@ -3045,13 +3063,13 @@
         <v>127</v>
       </c>
       <c r="B122" s="14">
-        <v>13.8326</v>
+        <v>13.9379</v>
       </c>
       <c r="C122" s="15">
         <v>0.07</v>
       </c>
       <c r="D122" s="16">
-        <v>15107843</v>
+        <v>16601729</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
@@ -3061,13 +3079,13 @@
         <v>128</v>
       </c>
       <c r="B123" s="14">
-        <v>13.8236</v>
+        <v>13.9288</v>
       </c>
       <c r="C123" s="15">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="D123" s="16">
-        <v>14970972</v>
+        <v>16602821</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -3077,13 +3095,13 @@
         <v>129</v>
       </c>
       <c r="B124" s="14">
-        <v>13.8241</v>
+        <v>13.9309</v>
       </c>
       <c r="C124" s="15">
-        <v>-0.28</v>
+        <v>0.38</v>
       </c>
       <c r="D124" s="16">
-        <v>15045700</v>
+        <v>16604572</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
@@ -3093,13 +3111,13 @@
         <v>130</v>
       </c>
       <c r="B125" s="14">
-        <v>13.8632</v>
+        <v>13.8785</v>
       </c>
       <c r="C125" s="15">
-        <v>-1.08</v>
+        <v>-0.14</v>
       </c>
       <c r="D125" s="16">
-        <v>15031857</v>
+        <v>16580643</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -3109,13 +3127,13 @@
         <v>131</v>
       </c>
       <c r="B126" s="14">
-        <v>14.014</v>
+        <v>13.8972</v>
       </c>
       <c r="C126" s="15">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="D126" s="16">
-        <v>14669668</v>
+        <v>16067893</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
@@ -3125,13 +3143,13 @@
         <v>132</v>
       </c>
       <c r="B127" s="14">
-        <v>13.9557</v>
+        <v>13.8471</v>
       </c>
       <c r="C127" s="15">
-        <v>1.17</v>
+        <v>0.11</v>
       </c>
       <c r="D127" s="16">
-        <v>14653804</v>
+        <v>15348175</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
@@ -3141,13 +3159,13 @@
         <v>133</v>
       </c>
       <c r="B128" s="14">
-        <v>13.7949</v>
+        <v>13.8326</v>
       </c>
       <c r="C128" s="15">
-        <v>-0.28</v>
+        <v>0.07</v>
       </c>
       <c r="D128" s="16">
-        <v>14652445</v>
+        <v>15107843</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
@@ -3157,13 +3175,13 @@
         <v>134</v>
       </c>
       <c r="B129" s="14">
-        <v>13.8331</v>
+        <v>13.8236</v>
       </c>
       <c r="C129" s="15">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="D129" s="16">
-        <v>14639361</v>
+        <v>14970972</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
@@ -3173,13 +3191,13 @@
         <v>135</v>
       </c>
       <c r="B130" s="14">
-        <v>13.9982</v>
+        <v>13.8241</v>
       </c>
       <c r="C130" s="15">
-        <v>1.11</v>
+        <v>-0.28</v>
       </c>
       <c r="D130" s="16">
-        <v>14636809</v>
+        <v>15045700</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
@@ -3189,13 +3207,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="14">
-        <v>13.845</v>
+        <v>13.8632</v>
       </c>
       <c r="C131" s="15">
-        <v>-1.07</v>
+        <v>-1.08</v>
       </c>
       <c r="D131" s="16">
-        <v>14433805</v>
+        <v>15031857</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
@@ -3205,13 +3223,13 @@
         <v>137</v>
       </c>
       <c r="B132" s="14">
-        <v>13.9953</v>
+        <v>14.014</v>
       </c>
       <c r="C132" s="15">
-        <v>-0.27</v>
+        <v>0.42</v>
       </c>
       <c r="D132" s="16">
-        <v>13989441</v>
+        <v>14669668</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
@@ -3221,13 +3239,13 @@
         <v>138</v>
       </c>
       <c r="B133" s="14">
-        <v>14.0336</v>
+        <v>13.9557</v>
       </c>
       <c r="C133" s="15">
-        <v>-0.38</v>
+        <v>1.17</v>
       </c>
       <c r="D133" s="16">
-        <v>13566681</v>
+        <v>14653804</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
@@ -3237,13 +3255,13 @@
         <v>139</v>
       </c>
       <c r="B134" s="14">
-        <v>14.087</v>
+        <v>13.7949</v>
       </c>
       <c r="C134" s="15">
-        <v>0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="D134" s="16">
-        <v>13137192</v>
+        <v>14652445</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
@@ -3253,13 +3271,13 @@
         <v>140</v>
       </c>
       <c r="B135" s="14">
-        <v>14.0394</v>
+        <v>13.8331</v>
       </c>
       <c r="C135" s="15">
-        <v>1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="D135" s="16">
-        <v>12985801</v>
+        <v>14639361</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
@@ -3269,13 +3287,13 @@
         <v>141</v>
       </c>
       <c r="B136" s="14">
-        <v>13.8773</v>
+        <v>13.9982</v>
       </c>
       <c r="C136" s="15">
-        <v>0.97</v>
+        <v>1.11</v>
       </c>
       <c r="D136" s="16">
-        <v>12941290</v>
+        <v>14636809</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
@@ -3285,13 +3303,13 @@
         <v>142</v>
       </c>
       <c r="B137" s="14">
-        <v>13.7443</v>
+        <v>13.845</v>
       </c>
       <c r="C137" s="15">
-        <v>0.04</v>
+        <v>-1.07</v>
       </c>
       <c r="D137" s="16">
-        <v>12972634</v>
+        <v>14433805</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
@@ -3301,13 +3319,13 @@
         <v>143</v>
       </c>
       <c r="B138" s="14">
-        <v>13.7392</v>
+        <v>13.9953</v>
       </c>
       <c r="C138" s="15">
-        <v>0.73</v>
+        <v>-0.27</v>
       </c>
       <c r="D138" s="16">
-        <v>12694568</v>
+        <v>13989441</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
@@ -3317,13 +3335,13 @@
         <v>144</v>
       </c>
       <c r="B139" s="14">
-        <v>13.6402</v>
+        <v>14.0336</v>
       </c>
       <c r="C139" s="15">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="D139" s="16">
-        <v>12659561</v>
+        <v>13566681</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
@@ -3333,13 +3351,13 @@
         <v>145</v>
       </c>
       <c r="B140" s="14">
-        <v>13.678</v>
+        <v>14.087</v>
       </c>
       <c r="C140" s="15">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="D140" s="16">
-        <v>12821290</v>
+        <v>13137192</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
@@ -3349,13 +3367,13 @@
         <v>146</v>
       </c>
       <c r="B141" s="14">
-        <v>13.6484</v>
+        <v>14.0394</v>
       </c>
       <c r="C141" s="15">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="D141" s="16">
-        <v>12815298</v>
+        <v>12985801</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
@@ -3365,13 +3383,13 @@
         <v>147</v>
       </c>
       <c r="B142" s="14">
-        <v>13.5523</v>
+        <v>13.8773</v>
       </c>
       <c r="C142" s="15">
-        <v>-0.16</v>
+        <v>0.97</v>
       </c>
       <c r="D142" s="16">
-        <v>12778173</v>
+        <v>12941290</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
@@ -3381,13 +3399,13 @@
         <v>148</v>
       </c>
       <c r="B143" s="14">
-        <v>13.5734</v>
+        <v>13.7443</v>
       </c>
       <c r="C143" s="15">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="D143" s="16">
-        <v>12525374</v>
+        <v>12972634</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
@@ -3397,13 +3415,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="14">
-        <v>13.5259</v>
+        <v>13.7392</v>
       </c>
       <c r="C144" s="15">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="D144" s="16">
-        <v>12222638</v>
+        <v>12694568</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
@@ -3413,13 +3431,13 @@
         <v>150</v>
       </c>
       <c r="B145" s="14">
-        <v>13.4447</v>
+        <v>13.6402</v>
       </c>
       <c r="C145" s="15">
-        <v>0.33</v>
+        <v>-0.28</v>
       </c>
       <c r="D145" s="16">
-        <v>11902533</v>
+        <v>12659561</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
@@ -3429,13 +3447,13 @@
         <v>151</v>
       </c>
       <c r="B146" s="14">
-        <v>13.4005</v>
+        <v>13.678</v>
       </c>
       <c r="C146" s="15">
         <v>0.22</v>
       </c>
       <c r="D146" s="16">
-        <v>11564711</v>
+        <v>12821290</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
@@ -3445,13 +3463,13 @@
         <v>152</v>
       </c>
       <c r="B147" s="14">
-        <v>13.3707</v>
+        <v>13.6484</v>
       </c>
       <c r="C147" s="15">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="D147" s="16">
-        <v>11491616</v>
+        <v>12815298</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
@@ -3461,13 +3479,13 @@
         <v>153</v>
       </c>
       <c r="B148" s="14">
-        <v>13.3256</v>
+        <v>13.5523</v>
       </c>
       <c r="C148" s="15">
-        <v>0.93</v>
+        <v>-0.16</v>
       </c>
       <c r="D148" s="16">
-        <v>11511148</v>
+        <v>12778173</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
@@ -3477,13 +3495,13 @@
         <v>154</v>
       </c>
       <c r="B149" s="14">
-        <v>13.2028</v>
+        <v>13.5734</v>
       </c>
       <c r="C149" s="15">
-        <v>-0.53</v>
+        <v>0.35</v>
       </c>
       <c r="D149" s="16">
-        <v>11462549</v>
+        <v>12525374</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
@@ -3493,13 +3511,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="14">
-        <v>13.2731</v>
+        <v>13.5259</v>
       </c>
       <c r="C150" s="15">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="D150" s="16">
-        <v>11252942</v>
+        <v>12222638</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
@@ -3509,13 +3527,13 @@
         <v>156</v>
       </c>
       <c r="B151" s="14">
-        <v>13.2446</v>
+        <v>13.4447</v>
       </c>
       <c r="C151" s="15">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="D151" s="16">
-        <v>11240222</v>
+        <v>11902533</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
@@ -3525,13 +3543,13 @@
         <v>157</v>
       </c>
       <c r="B152" s="14">
-        <v>13.1508</v>
+        <v>13.4005</v>
       </c>
       <c r="C152" s="15">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="D152" s="16">
-        <v>11279869</v>
+        <v>11564711</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
@@ -3541,13 +3559,13 @@
         <v>158</v>
       </c>
       <c r="B153" s="14">
-        <v>13.0979</v>
+        <v>13.3707</v>
       </c>
       <c r="C153" s="15">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
       <c r="D153" s="16">
-        <v>11319939</v>
+        <v>11491616</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
@@ -3557,13 +3575,13 @@
         <v>159</v>
       </c>
       <c r="B154" s="14">
-        <v>13.1255</v>
+        <v>13.3256</v>
       </c>
       <c r="C154" s="15">
-        <v>0.31</v>
+        <v>0.93</v>
       </c>
       <c r="D154" s="16">
-        <v>11273680</v>
+        <v>11511148</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
@@ -3573,13 +3591,13 @@
         <v>160</v>
       </c>
       <c r="B155" s="14">
-        <v>13.0855</v>
+        <v>13.2028</v>
       </c>
       <c r="C155" s="15">
-        <v>-1</v>
+        <v>-0.53</v>
       </c>
       <c r="D155" s="16">
-        <v>10907008</v>
+        <v>11462549</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
@@ -3589,13 +3607,13 @@
         <v>161</v>
       </c>
       <c r="B156" s="14">
-        <v>13.2179</v>
+        <v>13.2731</v>
       </c>
       <c r="C156" s="15">
-        <v>-0.62</v>
+        <v>0.22</v>
       </c>
       <c r="D156" s="16">
-        <v>10664204</v>
+        <v>11252942</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
@@ -3605,13 +3623,13 @@
         <v>162</v>
       </c>
       <c r="B157" s="14">
-        <v>13.3002</v>
+        <v>13.2446</v>
       </c>
       <c r="C157" s="15">
-        <v>0.97</v>
+        <v>0.71</v>
       </c>
       <c r="D157" s="16">
-        <v>9876428</v>
+        <v>11240222</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
@@ -3621,13 +3639,13 @@
         <v>163</v>
       </c>
       <c r="B158" s="14">
-        <v>13.1727</v>
+        <v>13.1508</v>
       </c>
       <c r="C158" s="15">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="D158" s="16">
-        <v>8896695</v>
+        <v>11279869</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
@@ -3637,13 +3655,13 @@
         <v>164</v>
       </c>
       <c r="B159" s="14">
-        <v>13.1256</v>
+        <v>13.0979</v>
       </c>
       <c r="C159" s="15">
-        <v>0.31</v>
+        <v>-0.21</v>
       </c>
       <c r="D159" s="16">
-        <v>8738282</v>
+        <v>11319939</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
@@ -3653,13 +3671,13 @@
         <v>165</v>
       </c>
       <c r="B160" s="14">
-        <v>13.0849</v>
+        <v>13.1255</v>
       </c>
       <c r="C160" s="15">
-        <v>-0.59</v>
+        <v>0.31</v>
       </c>
       <c r="D160" s="16">
-        <v>8668100</v>
+        <v>11273680</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
@@ -3669,13 +3687,13 @@
         <v>166</v>
       </c>
       <c r="B161" s="14">
-        <v>13.1621</v>
+        <v>13.0855</v>
       </c>
       <c r="C161" s="15">
-        <v>0.27</v>
+        <v>-1</v>
       </c>
       <c r="D161" s="16">
-        <v>8981828</v>
+        <v>10907008</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
@@ -3685,13 +3703,13 @@
         <v>167</v>
       </c>
       <c r="B162" s="14">
-        <v>13.1268</v>
+        <v>13.2179</v>
       </c>
       <c r="C162" s="15">
-        <v>0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="D162" s="16">
-        <v>7580892</v>
+        <v>10664204</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
@@ -3701,13 +3719,13 @@
         <v>168</v>
       </c>
       <c r="B163" s="14">
-        <v>13.0564</v>
+        <v>13.3002</v>
       </c>
       <c r="C163" s="15">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="D163" s="16">
-        <v>7496759</v>
+        <v>9876428</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
@@ -3717,13 +3735,13 @@
         <v>169</v>
       </c>
       <c r="B164" s="14">
-        <v>13.0298</v>
+        <v>13.1727</v>
       </c>
       <c r="C164" s="15">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="D164" s="16">
-        <v>7405096</v>
+        <v>8896695</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
@@ -3733,13 +3751,13 @@
         <v>170</v>
       </c>
       <c r="B165" s="14">
-        <v>13.0006</v>
+        <v>13.1256</v>
       </c>
       <c r="C165" s="15">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="D165" s="16">
-        <v>7348884</v>
+        <v>8738282</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
@@ -3749,13 +3767,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="14">
-        <v>12.9666</v>
+        <v>13.0849</v>
       </c>
       <c r="C166" s="15">
-        <v>1.15</v>
+        <v>-0.59</v>
       </c>
       <c r="D166" s="16">
-        <v>7204621</v>
+        <v>8668100</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
@@ -3765,13 +3783,13 @@
         <v>172</v>
       </c>
       <c r="B167" s="14">
-        <v>12.8192</v>
+        <v>13.1621</v>
       </c>
       <c r="C167" s="15">
-        <v>-0.67</v>
+        <v>0.27</v>
       </c>
       <c r="D167" s="16">
-        <v>6739403</v>
+        <v>8981828</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
@@ -3781,13 +3799,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="14">
-        <v>12.9052</v>
+        <v>13.1268</v>
       </c>
       <c r="C168" s="15">
-        <v>0.91</v>
+        <v>0.54</v>
       </c>
       <c r="D168" s="16">
-        <v>6150440</v>
+        <v>7580892</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
@@ -3797,13 +3815,13 @@
         <v>174</v>
       </c>
       <c r="B169" s="14">
-        <v>12.7893</v>
+        <v>13.0564</v>
       </c>
       <c r="C169" s="15">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="D169" s="16">
-        <v>5477565</v>
+        <v>7496759</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
@@ -3813,13 +3831,13 @@
         <v>175</v>
       </c>
       <c r="B170" s="14">
-        <v>12.7476</v>
+        <v>13.0298</v>
       </c>
       <c r="C170" s="15">
-        <v>-0.03</v>
+        <v>0.23</v>
       </c>
       <c r="D170" s="16">
-        <v>4610342</v>
+        <v>7405096</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
@@ -3829,13 +3847,13 @@
         <v>176</v>
       </c>
       <c r="B171" s="14">
-        <v>12.7519</v>
+        <v>13.0006</v>
       </c>
       <c r="C171" s="15">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="D171" s="16">
-        <v>4446149</v>
+        <v>7348884</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
@@ -3845,13 +3863,13 @@
         <v>177</v>
       </c>
       <c r="B172" s="14">
-        <v>12.6636</v>
+        <v>12.9666</v>
       </c>
       <c r="C172" s="15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="D172" s="16">
-        <v>4373755</v>
+        <v>7204621</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
@@ -3861,13 +3879,13 @@
         <v>178</v>
       </c>
       <c r="B173" s="14">
-        <v>12.5179</v>
+        <v>12.8192</v>
       </c>
       <c r="C173" s="15">
-        <v>2.49</v>
+        <v>-0.67</v>
       </c>
       <c r="D173" s="16">
-        <v>4232302</v>
+        <v>6739403</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
@@ -3877,13 +3895,13 @@
         <v>179</v>
       </c>
       <c r="B174" s="14">
-        <v>12.214</v>
+        <v>12.9052</v>
       </c>
       <c r="C174" s="15">
-        <v>-1.27</v>
+        <v>0.91</v>
       </c>
       <c r="D174" s="16">
-        <v>4038721</v>
+        <v>6150440</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
@@ -3893,13 +3911,13 @@
         <v>180</v>
       </c>
       <c r="B175" s="14">
-        <v>12.3707</v>
+        <v>12.7893</v>
       </c>
       <c r="C175" s="15">
-        <v>-0.87</v>
+        <v>0.33</v>
       </c>
       <c r="D175" s="16">
-        <v>3942311</v>
+        <v>5477565</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="12"/>
@@ -3909,13 +3927,13 @@
         <v>181</v>
       </c>
       <c r="B176" s="14">
-        <v>12.4788</v>
+        <v>12.7476</v>
       </c>
       <c r="C176" s="15">
-        <v>0.33</v>
+        <v>-0.03</v>
       </c>
       <c r="D176" s="16">
-        <v>3892723</v>
+        <v>4610342</v>
       </c>
       <c r="E176" s="12"/>
       <c r="F176" s="12"/>
@@ -3925,13 +3943,13 @@
         <v>182</v>
       </c>
       <c r="B177" s="14">
-        <v>12.4379</v>
+        <v>12.7519</v>
       </c>
       <c r="C177" s="15">
-        <v>2.22</v>
+        <v>0.7</v>
       </c>
       <c r="D177" s="16">
-        <v>3848519</v>
+        <v>4446149</v>
       </c>
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
@@ -3941,13 +3959,13 @@
         <v>183</v>
       </c>
       <c r="B178" s="14">
-        <v>12.1674</v>
+        <v>12.6636</v>
       </c>
       <c r="C178" s="15">
-        <v>0.53</v>
+        <v>1.16</v>
       </c>
       <c r="D178" s="16">
-        <v>3819107</v>
+        <v>4373755</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
@@ -3957,13 +3975,13 @@
         <v>184</v>
       </c>
       <c r="B179" s="14">
-        <v>12.1034</v>
+        <v>12.5179</v>
       </c>
       <c r="C179" s="15">
-        <v>0.15</v>
+        <v>2.49</v>
       </c>
       <c r="D179" s="16">
-        <v>3631676</v>
+        <v>4232302</v>
       </c>
       <c r="E179" s="12"/>
       <c r="F179" s="12"/>
@@ -3973,13 +3991,13 @@
         <v>185</v>
       </c>
       <c r="B180" s="14">
-        <v>12.0853</v>
+        <v>12.214</v>
       </c>
       <c r="C180" s="15">
-        <v>0.92</v>
+        <v>-1.27</v>
       </c>
       <c r="D180" s="16">
-        <v>3361434</v>
+        <v>4038721</v>
       </c>
       <c r="E180" s="12"/>
       <c r="F180" s="12"/>
@@ -3989,13 +4007,13 @@
         <v>186</v>
       </c>
       <c r="B181" s="14">
-        <v>11.9757</v>
+        <v>12.3707</v>
       </c>
       <c r="C181" s="15">
-        <v>0.41</v>
+        <v>-0.87</v>
       </c>
       <c r="D181" s="16">
-        <v>2938660</v>
+        <v>3942311</v>
       </c>
       <c r="E181" s="12"/>
       <c r="F181" s="12"/>
@@ -4005,13 +4023,13 @@
         <v>187</v>
       </c>
       <c r="B182" s="14">
-        <v>11.9265</v>
+        <v>12.4788</v>
       </c>
       <c r="C182" s="15">
-        <v>-0.67</v>
+        <v>0.33</v>
       </c>
       <c r="D182" s="16">
-        <v>2728134</v>
+        <v>3892723</v>
       </c>
       <c r="E182" s="12"/>
       <c r="F182" s="12"/>
@@ -4021,13 +4039,13 @@
         <v>188</v>
       </c>
       <c r="B183" s="14">
-        <v>12.0069</v>
+        <v>12.4379</v>
       </c>
       <c r="C183" s="15">
-        <v>0.2</v>
+        <v>2.22</v>
       </c>
       <c r="D183" s="16">
-        <v>2719630</v>
+        <v>3848519</v>
       </c>
       <c r="E183" s="12"/>
       <c r="F183" s="12"/>
@@ -4037,13 +4055,13 @@
         <v>189</v>
       </c>
       <c r="B184" s="14">
-        <v>11.9827</v>
+        <v>12.1674</v>
       </c>
       <c r="C184" s="15">
-        <v>-0.88</v>
+        <v>0.53</v>
       </c>
       <c r="D184" s="16">
-        <v>2688147</v>
+        <v>3819107</v>
       </c>
       <c r="E184" s="12"/>
       <c r="F184" s="12"/>
@@ -4053,13 +4071,13 @@
         <v>190</v>
       </c>
       <c r="B185" s="14">
-        <v>12.0885</v>
+        <v>12.1034</v>
       </c>
       <c r="C185" s="15">
-        <v>-0.57</v>
+        <v>0.15</v>
       </c>
       <c r="D185" s="16">
-        <v>2609918</v>
+        <v>3631676</v>
       </c>
       <c r="E185" s="12"/>
       <c r="F185" s="12"/>
@@ -4069,13 +4087,13 @@
         <v>191</v>
       </c>
       <c r="B186" s="14">
-        <v>12.1577</v>
+        <v>12.0853</v>
       </c>
       <c r="C186" s="15">
-        <v>-0.95</v>
+        <v>0.92</v>
       </c>
       <c r="D186" s="16">
-        <v>2382996</v>
+        <v>3361434</v>
       </c>
       <c r="E186" s="12"/>
       <c r="F186" s="12"/>
@@ -4085,13 +4103,13 @@
         <v>192</v>
       </c>
       <c r="B187" s="14">
-        <v>12.2745</v>
+        <v>11.9757</v>
       </c>
       <c r="C187" s="15">
-        <v>-0.52</v>
+        <v>0.41</v>
       </c>
       <c r="D187" s="16">
-        <v>2331599</v>
+        <v>2938660</v>
       </c>
       <c r="E187" s="12"/>
       <c r="F187" s="12"/>
@@ -4101,13 +4119,13 @@
         <v>193</v>
       </c>
       <c r="B188" s="14">
-        <v>12.3391</v>
+        <v>11.9265</v>
       </c>
       <c r="C188" s="15">
-        <v>-0.61</v>
+        <v>-0.67</v>
       </c>
       <c r="D188" s="16">
-        <v>2255473</v>
+        <v>2728134</v>
       </c>
       <c r="E188" s="12"/>
       <c r="F188" s="12"/>
@@ -4117,13 +4135,13 @@
         <v>194</v>
       </c>
       <c r="B189" s="14">
-        <v>12.4146</v>
+        <v>12.0069</v>
       </c>
       <c r="C189" s="15">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="D189" s="16">
-        <v>2190337</v>
+        <v>2719630</v>
       </c>
       <c r="E189" s="12"/>
       <c r="F189" s="12"/>
@@ -4133,13 +4151,13 @@
         <v>195</v>
       </c>
       <c r="B190" s="14">
-        <v>12.2069</v>
+        <v>11.9827</v>
       </c>
       <c r="C190" s="15">
-        <v>0.06</v>
+        <v>-0.88</v>
       </c>
       <c r="D190" s="16">
-        <v>2136945</v>
+        <v>2688147</v>
       </c>
       <c r="E190" s="12"/>
       <c r="F190" s="12"/>
@@ -4149,13 +4167,13 @@
         <v>196</v>
       </c>
       <c r="B191" s="14">
-        <v>12.2</v>
+        <v>12.0885</v>
       </c>
       <c r="C191" s="15">
-        <v>-0.03</v>
+        <v>-0.57</v>
       </c>
       <c r="D191" s="16">
-        <v>1912961</v>
+        <v>2609918</v>
       </c>
       <c r="E191" s="12"/>
       <c r="F191" s="12"/>
@@ -4165,13 +4183,13 @@
         <v>197</v>
       </c>
       <c r="B192" s="14">
-        <v>12.2039</v>
+        <v>12.1577</v>
       </c>
       <c r="C192" s="15">
-        <v>1.06</v>
+        <v>-0.95</v>
       </c>
       <c r="D192" s="16">
-        <v>1647911</v>
+        <v>2382996</v>
       </c>
       <c r="E192" s="12"/>
       <c r="F192" s="12"/>
@@ -4181,13 +4199,13 @@
         <v>198</v>
       </c>
       <c r="B193" s="14">
-        <v>12.0758</v>
+        <v>12.2745</v>
       </c>
       <c r="C193" s="15">
-        <v>0.22</v>
+        <v>-0.52</v>
       </c>
       <c r="D193" s="16">
-        <v>1294332</v>
+        <v>2331599</v>
       </c>
       <c r="E193" s="12"/>
       <c r="F193" s="12"/>
@@ -4197,13 +4215,13 @@
         <v>199</v>
       </c>
       <c r="B194" s="14">
-        <v>12.0493</v>
+        <v>12.3391</v>
       </c>
       <c r="C194" s="15">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="D194" s="16">
-        <v>1062837</v>
+        <v>2255473</v>
       </c>
       <c r="E194" s="12"/>
       <c r="F194" s="12"/>
@@ -4213,13 +4231,13 @@
         <v>200</v>
       </c>
       <c r="B195" s="14">
-        <v>12.0181</v>
+        <v>12.4146</v>
       </c>
       <c r="C195" s="15">
-        <v>0.78</v>
+        <v>1.7</v>
       </c>
       <c r="D195" s="16">
-        <v>928815</v>
+        <v>2190337</v>
       </c>
       <c r="E195" s="12"/>
       <c r="F195" s="12"/>
@@ -4229,13 +4247,13 @@
         <v>201</v>
       </c>
       <c r="B196" s="14">
-        <v>11.9249</v>
+        <v>12.2069</v>
       </c>
       <c r="C196" s="15">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="D196" s="16">
-        <v>848138</v>
+        <v>2136945</v>
       </c>
       <c r="E196" s="12"/>
       <c r="F196" s="12"/>
@@ -4245,13 +4263,13 @@
         <v>202</v>
       </c>
       <c r="B197" s="14">
-        <v>11.8533</v>
+        <v>12.2</v>
       </c>
       <c r="C197" s="15">
-        <v>-0.62</v>
+        <v>-0.03</v>
       </c>
       <c r="D197" s="16">
-        <v>767931</v>
+        <v>1912961</v>
       </c>
       <c r="E197" s="12"/>
       <c r="F197" s="12"/>
@@ -4261,13 +4279,13 @@
         <v>203</v>
       </c>
       <c r="B198" s="14">
-        <v>11.9267</v>
+        <v>12.2039</v>
       </c>
       <c r="C198" s="15">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="D198" s="16">
-        <v>661974</v>
+        <v>1647911</v>
       </c>
       <c r="E198" s="12"/>
       <c r="F198" s="12"/>
@@ -4277,13 +4295,13 @@
         <v>204</v>
       </c>
       <c r="B199" s="14">
-        <v>11.83</v>
+        <v>12.0758</v>
       </c>
       <c r="C199" s="15">
-        <v>-0.17</v>
+        <v>0.22</v>
       </c>
       <c r="D199" s="16">
-        <v>640811</v>
+        <v>1294332</v>
       </c>
       <c r="E199" s="12"/>
       <c r="F199" s="12"/>
@@ -4293,13 +4311,13 @@
         <v>205</v>
       </c>
       <c r="B200" s="14">
-        <v>11.85</v>
+        <v>12.0493</v>
       </c>
       <c r="C200" s="15">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="D200" s="16">
-        <v>612687</v>
+        <v>1062837</v>
       </c>
       <c r="E200" s="12"/>
       <c r="F200" s="12"/>
@@ -4309,13 +4327,13 @@
         <v>206</v>
       </c>
       <c r="B201" s="14">
-        <v>11.8</v>
+        <v>12.0181</v>
       </c>
       <c r="C201" s="15">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="D201" s="16">
-        <v>605714</v>
+        <v>928815</v>
       </c>
       <c r="E201" s="12"/>
       <c r="F201" s="12"/>
@@ -4325,13 +4343,13 @@
         <v>207</v>
       </c>
       <c r="B202" s="14">
-        <v>11.753</v>
+        <v>11.9249</v>
       </c>
       <c r="C202" s="15">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="D202" s="16">
-        <v>584101</v>
+        <v>848138</v>
       </c>
       <c r="E202" s="12"/>
       <c r="F202" s="12"/>
@@ -4341,13 +4359,13 @@
         <v>208</v>
       </c>
       <c r="B203" s="14">
-        <v>11.715</v>
+        <v>11.8533</v>
       </c>
       <c r="C203" s="15">
-        <v>0.75</v>
+        <v>-0.62</v>
       </c>
       <c r="D203" s="16">
-        <v>534600</v>
+        <v>767931</v>
       </c>
       <c r="E203" s="12"/>
       <c r="F203" s="12"/>
@@ -4357,13 +4375,13 @@
         <v>209</v>
       </c>
       <c r="B204" s="14">
-        <v>11.628</v>
+        <v>11.9267</v>
       </c>
       <c r="C204" s="15">
-        <v>-0.36</v>
+        <v>0.82</v>
       </c>
       <c r="D204" s="16">
-        <v>396802</v>
+        <v>661974</v>
       </c>
       <c r="E204" s="12"/>
       <c r="F204" s="12"/>
@@ -4373,13 +4391,13 @@
         <v>210</v>
       </c>
       <c r="B205" s="14">
-        <v>11.67</v>
+        <v>11.83</v>
       </c>
       <c r="C205" s="15">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="D205" s="16">
-        <v>265881</v>
+        <v>640811</v>
       </c>
       <c r="E205" s="12"/>
       <c r="F205" s="12"/>
@@ -4389,13 +4407,13 @@
         <v>211</v>
       </c>
       <c r="B206" s="14">
-        <v>11.683</v>
+        <v>11.85</v>
       </c>
       <c r="C206" s="15">
-        <v>-0.18</v>
+        <v>0.42</v>
       </c>
       <c r="D206" s="16">
-        <v>244798</v>
+        <v>612687</v>
       </c>
       <c r="E206" s="12"/>
       <c r="F206" s="12"/>
@@ -4405,13 +4423,13 @@
         <v>212</v>
       </c>
       <c r="B207" s="14">
-        <v>11.704</v>
+        <v>11.8</v>
       </c>
       <c r="C207" s="15">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="D207" s="16">
-        <v>227751</v>
+        <v>605714</v>
       </c>
       <c r="E207" s="12"/>
       <c r="F207" s="12"/>
@@ -4421,13 +4439,13 @@
         <v>213</v>
       </c>
       <c r="B208" s="14">
-        <v>11.607</v>
+        <v>11.753</v>
       </c>
       <c r="C208" s="15">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="D208" s="16">
-        <v>214864</v>
+        <v>584101</v>
       </c>
       <c r="E208" s="12"/>
       <c r="F208" s="12"/>
@@ -4437,13 +4455,13 @@
         <v>214</v>
       </c>
       <c r="B209" s="14">
-        <v>11.604</v>
+        <v>11.715</v>
       </c>
       <c r="C209" s="15">
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
       <c r="D209" s="16">
-        <v>173999</v>
+        <v>534600</v>
       </c>
       <c r="E209" s="12"/>
       <c r="F209" s="12"/>
@@ -4453,13 +4471,13 @@
         <v>215</v>
       </c>
       <c r="B210" s="14">
-        <v>11.496</v>
+        <v>11.628</v>
       </c>
       <c r="C210" s="15">
-        <v>1.43</v>
+        <v>-0.36</v>
       </c>
       <c r="D210" s="16">
-        <v>158951</v>
+        <v>396802</v>
       </c>
       <c r="E210" s="12"/>
       <c r="F210" s="12"/>
@@ -4469,13 +4487,13 @@
         <v>216</v>
       </c>
       <c r="B211" s="14">
-        <v>11.334</v>
+        <v>11.67</v>
       </c>
       <c r="C211" s="15">
-        <v>3.6</v>
+        <v>-0.11</v>
       </c>
       <c r="D211" s="16">
-        <v>153245</v>
+        <v>265881</v>
       </c>
       <c r="E211" s="12"/>
       <c r="F211" s="12"/>
@@ -4485,13 +4503,13 @@
         <v>217</v>
       </c>
       <c r="B212" s="14">
-        <v>10.94</v>
+        <v>11.683</v>
       </c>
       <c r="C212" s="15">
-        <v>0.52</v>
+        <v>-0.18</v>
       </c>
       <c r="D212" s="16">
-        <v>150460</v>
+        <v>244798</v>
       </c>
       <c r="E212" s="12"/>
       <c r="F212" s="12"/>
@@ -4501,13 +4519,13 @@
         <v>218</v>
       </c>
       <c r="B213" s="14">
-        <v>10.884</v>
+        <v>11.704</v>
       </c>
       <c r="C213" s="15">
-        <v>1.57</v>
+        <v>0.84</v>
       </c>
       <c r="D213" s="16">
-        <v>149975</v>
+        <v>227751</v>
       </c>
       <c r="E213" s="12"/>
       <c r="F213" s="12"/>
@@ -4517,13 +4535,13 @@
         <v>219</v>
       </c>
       <c r="B214" s="14">
-        <v>10.716</v>
+        <v>11.607</v>
       </c>
       <c r="C214" s="15">
-        <v>0.37</v>
+        <v>0.03</v>
       </c>
       <c r="D214" s="16">
-        <v>146802</v>
+        <v>214864</v>
       </c>
       <c r="E214" s="12"/>
       <c r="F214" s="12"/>
@@ -4533,13 +4551,13 @@
         <v>220</v>
       </c>
       <c r="B215" s="14">
-        <v>10.677</v>
+        <v>11.604</v>
       </c>
       <c r="C215" s="15">
-        <v>-0.43</v>
+        <v>0.94</v>
       </c>
       <c r="D215" s="16">
-        <v>55851</v>
+        <v>173999</v>
       </c>
       <c r="E215" s="12"/>
       <c r="F215" s="12"/>
@@ -4549,13 +4567,13 @@
         <v>221</v>
       </c>
       <c r="B216" s="14">
-        <v>10.723</v>
+        <v>11.496</v>
       </c>
       <c r="C216" s="15">
-        <v>-0.94</v>
+        <v>1.43</v>
       </c>
       <c r="D216" s="16">
-        <v>55484</v>
+        <v>158951</v>
       </c>
       <c r="E216" s="12"/>
       <c r="F216" s="12"/>
@@ -4565,13 +4583,13 @@
         <v>222</v>
       </c>
       <c r="B217" s="14">
-        <v>10.825</v>
+        <v>11.334</v>
       </c>
       <c r="C217" s="15">
-        <v>-1.17</v>
+        <v>3.6</v>
       </c>
       <c r="D217" s="16">
-        <v>53984</v>
+        <v>153245</v>
       </c>
       <c r="E217" s="12"/>
       <c r="F217" s="12"/>
@@ -4581,13 +4599,13 @@
         <v>223</v>
       </c>
       <c r="B218" s="14">
-        <v>10.953</v>
+        <v>10.94</v>
       </c>
       <c r="C218" s="15">
-        <v>-0.73</v>
+        <v>0.52</v>
       </c>
       <c r="D218" s="16">
-        <v>49996</v>
+        <v>150460</v>
       </c>
       <c r="E218" s="12"/>
       <c r="F218" s="12"/>
@@ -4597,13 +4615,13 @@
         <v>224</v>
       </c>
       <c r="B219" s="14">
-        <v>11.033</v>
+        <v>10.884</v>
       </c>
       <c r="C219" s="15">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="D219" s="16">
-        <v>46812</v>
+        <v>149975</v>
       </c>
       <c r="E219" s="12"/>
       <c r="F219" s="12"/>
@@ -4613,13 +4631,13 @@
         <v>225</v>
       </c>
       <c r="B220" s="14">
-        <v>10.914</v>
+        <v>10.716</v>
       </c>
       <c r="C220" s="15">
-        <v>1.9</v>
+        <v>0.37</v>
       </c>
       <c r="D220" s="16">
-        <v>46623</v>
+        <v>146802</v>
       </c>
       <c r="E220" s="12"/>
       <c r="F220" s="12"/>
@@ -4629,13 +4647,13 @@
         <v>226</v>
       </c>
       <c r="B221" s="14">
-        <v>10.711</v>
+        <v>10.677</v>
       </c>
       <c r="C221" s="15">
-        <v>-0.5</v>
+        <v>-0.43</v>
       </c>
       <c r="D221" s="16">
-        <v>43430</v>
+        <v>55851</v>
       </c>
       <c r="E221" s="12"/>
       <c r="F221" s="12"/>
@@ -4645,13 +4663,13 @@
         <v>227</v>
       </c>
       <c r="B222" s="14">
-        <v>10.765</v>
+        <v>10.723</v>
       </c>
       <c r="C222" s="15">
-        <v>0.8</v>
+        <v>-0.94</v>
       </c>
       <c r="D222" s="16">
-        <v>40192</v>
+        <v>55484</v>
       </c>
       <c r="E222" s="12"/>
       <c r="F222" s="12"/>
@@ -4661,13 +4679,13 @@
         <v>228</v>
       </c>
       <c r="B223" s="14">
-        <v>10.68</v>
+        <v>10.825</v>
       </c>
       <c r="C223" s="15">
-        <v>0.78</v>
+        <v>-1.17</v>
       </c>
       <c r="D223" s="16">
-        <v>40205</v>
+        <v>53984</v>
       </c>
       <c r="E223" s="12"/>
       <c r="F223" s="12"/>
@@ -4677,13 +4695,13 @@
         <v>229</v>
       </c>
       <c r="B224" s="14">
-        <v>10.597</v>
+        <v>10.953</v>
       </c>
       <c r="C224" s="15">
-        <v>-0.13</v>
+        <v>-0.73</v>
       </c>
       <c r="D224" s="16">
-        <v>39767</v>
+        <v>49996</v>
       </c>
       <c r="E224" s="12"/>
       <c r="F224" s="12"/>
@@ -4693,13 +4711,13 @@
         <v>230</v>
       </c>
       <c r="B225" s="14">
-        <v>10.611</v>
+        <v>11.033</v>
       </c>
       <c r="C225" s="15">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="D225" s="16">
-        <v>40015</v>
+        <v>46812</v>
       </c>
       <c r="E225" s="12"/>
       <c r="F225" s="12"/>
@@ -4709,13 +4727,13 @@
         <v>231</v>
       </c>
       <c r="B226" s="14">
-        <v>10.532</v>
+        <v>10.914</v>
       </c>
       <c r="C226" s="15">
-        <v>1.07</v>
+        <v>1.9</v>
       </c>
       <c r="D226" s="16">
-        <v>39952</v>
+        <v>46623</v>
       </c>
       <c r="E226" s="12"/>
       <c r="F226" s="12"/>
@@ -4725,13 +4743,13 @@
         <v>232</v>
       </c>
       <c r="B227" s="14">
-        <v>10.421</v>
+        <v>10.711</v>
       </c>
       <c r="C227" s="15">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="D227" s="16">
-        <v>40169</v>
+        <v>43430</v>
       </c>
       <c r="E227" s="12"/>
       <c r="F227" s="12"/>
@@ -4741,13 +4759,13 @@
         <v>233</v>
       </c>
       <c r="B228" s="14">
-        <v>10.472</v>
+        <v>10.765</v>
       </c>
       <c r="C228" s="15">
-        <v>-0.32</v>
+        <v>0.8</v>
       </c>
       <c r="D228" s="16">
-        <v>38333</v>
+        <v>40192</v>
       </c>
       <c r="E228" s="12"/>
       <c r="F228" s="12"/>
@@ -4757,13 +4775,13 @@
         <v>234</v>
       </c>
       <c r="B229" s="14">
-        <v>10.506</v>
+        <v>10.68</v>
       </c>
       <c r="C229" s="15">
-        <v>-0.46</v>
+        <v>0.78</v>
       </c>
       <c r="D229" s="16">
-        <v>38694</v>
+        <v>40205</v>
       </c>
       <c r="E229" s="12"/>
       <c r="F229" s="12"/>
@@ -4773,13 +4791,13 @@
         <v>235</v>
       </c>
       <c r="B230" s="14">
-        <v>10.554</v>
+        <v>10.597</v>
       </c>
       <c r="C230" s="15">
-        <v>0.23</v>
+        <v>-0.13</v>
       </c>
       <c r="D230" s="16">
-        <v>37907</v>
+        <v>39767</v>
       </c>
       <c r="E230" s="12"/>
       <c r="F230" s="12"/>
@@ -4789,13 +4807,13 @@
         <v>236</v>
       </c>
       <c r="B231" s="14">
-        <v>10.53</v>
+        <v>10.611</v>
       </c>
       <c r="C231" s="15">
-        <v>0.17</v>
+        <v>0.75</v>
       </c>
       <c r="D231" s="16">
-        <v>36650</v>
+        <v>40015</v>
       </c>
       <c r="E231" s="12"/>
       <c r="F231" s="12"/>
@@ -4805,13 +4823,13 @@
         <v>237</v>
       </c>
       <c r="B232" s="14">
-        <v>10.512</v>
+        <v>10.532</v>
       </c>
       <c r="C232" s="15">
-        <v>-0.19</v>
+        <v>1.07</v>
       </c>
       <c r="D232" s="16">
-        <v>34921</v>
+        <v>39952</v>
       </c>
       <c r="E232" s="12"/>
       <c r="F232" s="12"/>
@@ -4821,13 +4839,13 @@
         <v>238</v>
       </c>
       <c r="B233" s="14">
-        <v>10.532</v>
+        <v>10.421</v>
       </c>
       <c r="C233" s="15">
-        <v>-0.64</v>
+        <v>-0.49</v>
       </c>
       <c r="D233" s="16">
-        <v>33255</v>
+        <v>40169</v>
       </c>
       <c r="E233" s="12"/>
       <c r="F233" s="12"/>
@@ -4837,13 +4855,13 @@
         <v>239</v>
       </c>
       <c r="B234" s="14">
-        <v>10.6</v>
+        <v>10.472</v>
       </c>
       <c r="C234" s="15">
-        <v>0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="D234" s="16">
-        <v>32711</v>
+        <v>38333</v>
       </c>
       <c r="E234" s="12"/>
       <c r="F234" s="12"/>
@@ -4853,13 +4871,13 @@
         <v>240</v>
       </c>
       <c r="B235" s="14">
-        <v>10.54</v>
+        <v>10.506</v>
       </c>
       <c r="C235" s="15">
-        <v>-0.47</v>
+        <v>-0.46</v>
       </c>
       <c r="D235" s="16">
-        <v>33378</v>
+        <v>38694</v>
       </c>
       <c r="E235" s="12"/>
       <c r="F235" s="12"/>
@@ -4869,13 +4887,13 @@
         <v>241</v>
       </c>
       <c r="B236" s="14">
-        <v>10.59</v>
+        <v>10.554</v>
       </c>
       <c r="C236" s="15">
-        <v>0.48</v>
+        <v>0.23</v>
       </c>
       <c r="D236" s="16">
-        <v>34091</v>
+        <v>37907</v>
       </c>
       <c r="E236" s="12"/>
       <c r="F236" s="12"/>
@@ -4885,13 +4903,13 @@
         <v>242</v>
       </c>
       <c r="B237" s="14">
-        <v>10.539</v>
+        <v>10.53</v>
       </c>
       <c r="C237" s="15">
-        <v>0.59</v>
+        <v>0.17</v>
       </c>
       <c r="D237" s="16">
-        <v>34184</v>
+        <v>36650</v>
       </c>
       <c r="E237" s="12"/>
       <c r="F237" s="12"/>
@@ -4901,13 +4919,13 @@
         <v>243</v>
       </c>
       <c r="B238" s="14">
-        <v>10.477</v>
+        <v>10.512</v>
       </c>
       <c r="C238" s="15">
-        <v>0.53</v>
+        <v>-0.19</v>
       </c>
       <c r="D238" s="16">
-        <v>34385</v>
+        <v>34921</v>
       </c>
       <c r="E238" s="12"/>
       <c r="F238" s="12"/>
@@ -4917,13 +4935,13 @@
         <v>244</v>
       </c>
       <c r="B239" s="14">
-        <v>10.422</v>
+        <v>10.532</v>
       </c>
       <c r="C239" s="15">
-        <v>-0.55</v>
+        <v>-0.64</v>
       </c>
       <c r="D239" s="16">
-        <v>33911</v>
+        <v>33255</v>
       </c>
       <c r="E239" s="12"/>
       <c r="F239" s="12"/>
@@ -4933,13 +4951,13 @@
         <v>245</v>
       </c>
       <c r="B240" s="14">
-        <v>10.48</v>
+        <v>10.6</v>
       </c>
       <c r="C240" s="15">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="D240" s="16">
-        <v>33624</v>
+        <v>32711</v>
       </c>
       <c r="E240" s="12"/>
       <c r="F240" s="12"/>
@@ -4949,13 +4967,13 @@
         <v>246</v>
       </c>
       <c r="B241" s="14">
-        <v>10.402</v>
+        <v>10.54</v>
       </c>
       <c r="C241" s="15">
-        <v>-0.35</v>
+        <v>-0.47</v>
       </c>
       <c r="D241" s="16">
-        <v>22494</v>
+        <v>33378</v>
       </c>
       <c r="E241" s="12"/>
       <c r="F241" s="12"/>
@@ -4965,13 +4983,13 @@
         <v>247</v>
       </c>
       <c r="B242" s="14">
-        <v>10.438</v>
+        <v>10.59</v>
       </c>
       <c r="C242" s="15">
-        <v>-0.95</v>
+        <v>0.48</v>
       </c>
       <c r="D242" s="16">
-        <v>16869</v>
+        <v>34091</v>
       </c>
       <c r="E242" s="12"/>
       <c r="F242" s="12"/>
@@ -4981,13 +4999,13 @@
         <v>248</v>
       </c>
       <c r="B243" s="14">
-        <v>10.538</v>
+        <v>10.539</v>
       </c>
       <c r="C243" s="15">
-        <v>0.08</v>
+        <v>0.59</v>
       </c>
       <c r="D243" s="16">
-        <v>16869</v>
+        <v>34184</v>
       </c>
       <c r="E243" s="12"/>
       <c r="F243" s="12"/>
@@ -4997,13 +5015,13 @@
         <v>249</v>
       </c>
       <c r="B244" s="14">
-        <v>10.53</v>
+        <v>10.477</v>
       </c>
       <c r="C244" s="15">
-        <v>-0.38</v>
+        <v>0.53</v>
       </c>
       <c r="D244" s="16">
-        <v>17496</v>
+        <v>34385</v>
       </c>
       <c r="E244" s="12"/>
       <c r="F244" s="12"/>
@@ -5013,13 +5031,13 @@
         <v>250</v>
       </c>
       <c r="B245" s="14">
-        <v>10.57</v>
+        <v>10.422</v>
       </c>
       <c r="C245" s="15">
-        <v>0.17</v>
+        <v>-0.55</v>
       </c>
       <c r="D245" s="16">
-        <v>17496</v>
+        <v>33911</v>
       </c>
       <c r="E245" s="12"/>
       <c r="F245" s="12"/>
@@ -5029,13 +5047,13 @@
         <v>251</v>
       </c>
       <c r="B246" s="14">
-        <v>10.552</v>
+        <v>10.48</v>
       </c>
       <c r="C246" s="15">
-        <v>0.06</v>
+        <v>0.75</v>
       </c>
       <c r="D246" s="16">
-        <v>18388</v>
+        <v>33624</v>
       </c>
       <c r="E246" s="12"/>
       <c r="F246" s="12"/>
@@ -5045,13 +5063,13 @@
         <v>252</v>
       </c>
       <c r="B247" s="14">
-        <v>10.546</v>
+        <v>10.402</v>
       </c>
       <c r="C247" s="15">
-        <v>-0.78</v>
+        <v>-0.35</v>
       </c>
       <c r="D247" s="16">
-        <v>18296</v>
+        <v>22494</v>
       </c>
       <c r="E247" s="12"/>
       <c r="F247" s="12"/>
@@ -5061,13 +5079,13 @@
         <v>253</v>
       </c>
       <c r="B248" s="14">
-        <v>10.629</v>
+        <v>10.438</v>
       </c>
       <c r="C248" s="15">
-        <v>-0.13</v>
+        <v>-0.95</v>
       </c>
       <c r="D248" s="16">
-        <v>18525</v>
+        <v>16869</v>
       </c>
       <c r="E248" s="12"/>
       <c r="F248" s="12"/>
@@ -5077,13 +5095,13 @@
         <v>254</v>
       </c>
       <c r="B249" s="14">
-        <v>10.643</v>
+        <v>10.538</v>
       </c>
       <c r="C249" s="15">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
       <c r="D249" s="16">
-        <v>18764</v>
+        <v>16869</v>
       </c>
       <c r="E249" s="12"/>
       <c r="F249" s="12"/>
@@ -5093,13 +5111,13 @@
         <v>255</v>
       </c>
       <c r="B250" s="14">
-        <v>10.603</v>
+        <v>10.53</v>
       </c>
       <c r="C250" s="15">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="D250" s="16">
-        <v>18783</v>
+        <v>17496</v>
       </c>
       <c r="E250" s="12"/>
       <c r="F250" s="12"/>
@@ -5109,13 +5127,13 @@
         <v>256</v>
       </c>
       <c r="B251" s="14">
-        <v>10.637</v>
+        <v>10.57</v>
       </c>
       <c r="C251" s="15">
-        <v>0.85</v>
+        <v>0.17</v>
       </c>
       <c r="D251" s="16">
-        <v>18552</v>
+        <v>17496</v>
       </c>
       <c r="E251" s="12"/>
       <c r="F251" s="12"/>
@@ -5125,13 +5143,13 @@
         <v>257</v>
       </c>
       <c r="B252" s="14">
-        <v>10.547</v>
+        <v>10.552</v>
       </c>
       <c r="C252" s="15">
-        <v>0.46</v>
+        <v>0.06</v>
       </c>
       <c r="D252" s="16">
-        <v>17764</v>
+        <v>18388</v>
       </c>
       <c r="E252" s="12"/>
       <c r="F252" s="12"/>
@@ -5141,13 +5159,13 @@
         <v>258</v>
       </c>
       <c r="B253" s="14">
-        <v>10.499</v>
+        <v>10.546</v>
       </c>
       <c r="C253" s="15">
-        <v>1.52</v>
+        <v>-0.78</v>
       </c>
       <c r="D253" s="16">
-        <v>14538</v>
+        <v>18296</v>
       </c>
       <c r="E253" s="12"/>
       <c r="F253" s="12"/>
@@ -5157,13 +5175,13 @@
         <v>259</v>
       </c>
       <c r="B254" s="14">
-        <v>10.342</v>
+        <v>10.629</v>
       </c>
       <c r="C254" s="15">
-        <v>0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="D254" s="16">
-        <v>9092</v>
+        <v>18525</v>
       </c>
       <c r="E254" s="12"/>
       <c r="F254" s="12"/>
@@ -5173,13 +5191,13 @@
         <v>260</v>
       </c>
       <c r="B255" s="14">
-        <v>10.327</v>
+        <v>10.643</v>
       </c>
       <c r="C255" s="15">
-        <v>-0.31</v>
+        <v>0.38</v>
       </c>
       <c r="D255" s="16">
-        <v>8762</v>
+        <v>18764</v>
       </c>
       <c r="E255" s="12"/>
       <c r="F255" s="12"/>
@@ -5189,13 +5207,13 @@
         <v>261</v>
       </c>
       <c r="B256" s="14">
-        <v>10.359</v>
+        <v>10.603</v>
       </c>
       <c r="C256" s="15">
-        <v>0.51</v>
+        <v>-0.32</v>
       </c>
       <c r="D256" s="16">
-        <v>8762</v>
+        <v>18783</v>
       </c>
       <c r="E256" s="12"/>
       <c r="F256" s="12"/>
@@ -5205,13 +5223,13 @@
         <v>262</v>
       </c>
       <c r="B257" s="14">
-        <v>10.306</v>
+        <v>10.637</v>
       </c>
       <c r="C257" s="15">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="D257" s="16">
-        <v>9357</v>
+        <v>18552</v>
       </c>
       <c r="E257" s="12"/>
       <c r="F257" s="12"/>
@@ -5221,13 +5239,13 @@
         <v>263</v>
       </c>
       <c r="B258" s="14">
-        <v>10.287</v>
+        <v>10.547</v>
       </c>
       <c r="C258" s="15">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="D258" s="16">
-        <v>9357</v>
+        <v>17764</v>
       </c>
       <c r="E258" s="12"/>
       <c r="F258" s="12"/>
@@ -5237,13 +5255,13 @@
         <v>264</v>
       </c>
       <c r="B259" s="14">
-        <v>10.214</v>
+        <v>10.499</v>
       </c>
       <c r="C259" s="15">
-        <v>0.64</v>
+        <v>1.52</v>
       </c>
       <c r="D259" s="16">
-        <v>9558</v>
+        <v>14538</v>
       </c>
       <c r="E259" s="12"/>
       <c r="F259" s="12"/>
@@ -5253,13 +5271,13 @@
         <v>265</v>
       </c>
       <c r="B260" s="14">
-        <v>10.149</v>
+        <v>10.342</v>
       </c>
       <c r="C260" s="15">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="D260" s="16">
-        <v>9616</v>
+        <v>9092</v>
       </c>
       <c r="E260" s="12"/>
       <c r="F260" s="12"/>
@@ -5269,13 +5287,13 @@
         <v>266</v>
       </c>
       <c r="B261" s="14">
-        <v>10.095</v>
+        <v>10.327</v>
       </c>
       <c r="C261" s="15">
-        <v>0.8</v>
+        <v>-0.31</v>
       </c>
       <c r="D261" s="16">
-        <v>10127</v>
+        <v>8762</v>
       </c>
       <c r="E261" s="12"/>
       <c r="F261" s="12"/>
@@ -5285,13 +5303,13 @@
         <v>267</v>
       </c>
       <c r="B262" s="14">
-        <v>10.015</v>
+        <v>10.359</v>
       </c>
       <c r="C262" s="15">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="D262" s="16">
-        <v>7988</v>
+        <v>8762</v>
       </c>
       <c r="E262" s="12"/>
       <c r="F262" s="12"/>
@@ -5301,13 +5319,13 @@
         <v>268</v>
       </c>
       <c r="B263" s="14">
-        <v>9.97</v>
+        <v>10.306</v>
       </c>
       <c r="C263" s="15">
-        <v>-0.31</v>
+        <v>0.19</v>
       </c>
       <c r="D263" s="16">
-        <v>8865</v>
+        <v>9357</v>
       </c>
       <c r="E263" s="12"/>
       <c r="F263" s="12"/>
@@ -5317,13 +5335,13 @@
         <v>269</v>
       </c>
       <c r="B264" s="14">
-        <v>10.001</v>
+        <v>10.287</v>
       </c>
       <c r="C264" s="15">
-        <v>0.18</v>
+        <v>0.72</v>
       </c>
       <c r="D264" s="16">
-        <v>2189</v>
+        <v>9357</v>
       </c>
       <c r="E264" s="12"/>
       <c r="F264" s="12"/>
@@ -5333,13 +5351,13 @@
         <v>270</v>
       </c>
       <c r="B265" s="14">
-        <v>9.983</v>
+        <v>10.214</v>
       </c>
       <c r="C265" s="15">
-        <v>-1.39</v>
+        <v>0.64</v>
       </c>
       <c r="D265" s="16">
-        <v>500</v>
+        <v>9558</v>
       </c>
       <c r="E265" s="12"/>
       <c r="F265" s="12"/>
@@ -5349,13 +5367,13 @@
         <v>271</v>
       </c>
       <c r="B266" s="14">
-        <v>10.124</v>
+        <v>10.149</v>
       </c>
       <c r="C266" s="15">
-        <v>1.24</v>
+        <v>0.54</v>
       </c>
       <c r="D266" s="16">
-        <v>500</v>
+        <v>9616</v>
       </c>
       <c r="E266" s="12"/>
       <c r="F266" s="12"/>
@@ -5365,29 +5383,125 @@
         <v>272</v>
       </c>
       <c r="B267" s="14">
-        <v>10</v>
-      </c>
-      <c r="C267" s="17" t="s">
-        <v>273</v>
+        <v>10.095</v>
+      </c>
+      <c r="C267" s="15">
+        <v>0.8</v>
       </c>
       <c r="D267" s="16">
-        <v>0</v>
+        <v>10127</v>
       </c>
       <c r="E267" s="12"/>
       <c r="F267" s="12"/>
     </row>
-    <row r="268" ht="35" customHeight="1">
-      <c r="A268" s="18" t="s">
+    <row r="268" s="12" customFormat="1">
+      <c r="A268" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B268" s="14">
+        <v>10.015</v>
+      </c>
+      <c r="C268" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="D268" s="16">
+        <v>7988</v>
+      </c>
+      <c r="E268" s="12"/>
+      <c r="F268" s="12"/>
+    </row>
+    <row r="269" s="12" customFormat="1">
+      <c r="A269" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="B268" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C268" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="D268" s="18" t="s">
-        <v>274</v>
+      <c r="B269" s="14">
+        <v>9.97</v>
+      </c>
+      <c r="C269" s="15">
+        <v>-0.31</v>
+      </c>
+      <c r="D269" s="16">
+        <v>8865</v>
+      </c>
+      <c r="E269" s="12"/>
+      <c r="F269" s="12"/>
+    </row>
+    <row r="270" s="12" customFormat="1">
+      <c r="A270" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B270" s="14">
+        <v>10.001</v>
+      </c>
+      <c r="C270" s="15">
+        <v>0.18</v>
+      </c>
+      <c r="D270" s="16">
+        <v>2189</v>
+      </c>
+      <c r="E270" s="12"/>
+      <c r="F270" s="12"/>
+    </row>
+    <row r="271" s="12" customFormat="1">
+      <c r="A271" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="B271" s="14">
+        <v>9.983</v>
+      </c>
+      <c r="C271" s="15">
+        <v>-1.39</v>
+      </c>
+      <c r="D271" s="16">
+        <v>500</v>
+      </c>
+      <c r="E271" s="12"/>
+      <c r="F271" s="12"/>
+    </row>
+    <row r="272" s="12" customFormat="1">
+      <c r="A272" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B272" s="14">
+        <v>10.124</v>
+      </c>
+      <c r="C272" s="15">
+        <v>1.24</v>
+      </c>
+      <c r="D272" s="16">
+        <v>500</v>
+      </c>
+      <c r="E272" s="12"/>
+      <c r="F272" s="12"/>
+    </row>
+    <row r="273" s="12" customFormat="1">
+      <c r="A273" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B273" s="14">
+        <v>10</v>
+      </c>
+      <c r="C273" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="D273" s="16">
+        <v>0</v>
+      </c>
+      <c r="E273" s="12"/>
+      <c r="F273" s="12"/>
+    </row>
+    <row r="274" ht="35" customHeight="1">
+      <c r="A274" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="B274" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C274" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D274" s="18" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5403,18 +5517,18 @@
     <mergeCell ref="E4:E4"/>
     <mergeCell ref="E5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A268:D268"/>
+    <mergeCell ref="A274:D274"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Historique Cours'!A268" display="Se rendre en bas du document"/>
-    <hyperlink ref="B6" location="'Historique Cours'!A268" display="Se rendre en bas du document"/>
-    <hyperlink ref="C6" location="'Historique Cours'!A268" display="Se rendre en bas du document"/>
-    <hyperlink ref="D6" location="'Historique Cours'!A268" display="Se rendre en bas du document"/>
-    <hyperlink ref="E6" location="'Historique Cours'!A268" display="Se rendre en bas du document"/>
-    <hyperlink ref="A268" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="B268" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="C268" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="D268" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="A6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
+    <hyperlink ref="B6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
+    <hyperlink ref="C6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
+    <hyperlink ref="D6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
+    <hyperlink ref="E6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
+    <hyperlink ref="A274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="B274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="C274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="D274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
   </hyperlinks>
   <headerFooter/>
   <tableParts>

--- a/data/SOCIAL ACTIVE TEMPERE SOLIDAIRE.xlsx
+++ b/data/SOCIAL ACTIVE TEMPERE SOLIDAIRE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
   <si>
     <t>Historique Cours</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Date d'export</t>
   </si>
   <si>
-    <t>21/04/2026</t>
+    <t>21/10/2026</t>
   </si>
   <si>
     <t>Valeur :</t>
@@ -51,6 +51,24 @@
   </si>
   <si>
     <t>Volume</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
   </si>
   <si>
     <t>31/03/2026</t>
@@ -1111,8 +1129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D273" headerRowCount="1">
-  <autoFilter ref="A7:D273"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D279" headerRowCount="1">
+  <autoFilter ref="A7:D279"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Date de cotation"/>
     <tableColumn id="2" name="Dernier cours en EUR"/>
@@ -1125,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1" style="1"/>
@@ -1239,13 +1257,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="14">
-        <v>15.4606</v>
+        <v>15.8493</v>
       </c>
       <c r="C8" s="15">
-        <v>-4.14</v>
+        <v>-1.41</v>
       </c>
       <c r="D8" s="16">
-        <v>25607229</v>
+        <v>25513641</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1255,13 +1273,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="14">
-        <v>16.1277</v>
+        <v>16.0757</v>
       </c>
       <c r="C9" s="15">
-        <v>1.38</v>
+        <v>-0.24</v>
       </c>
       <c r="D9" s="16">
-        <v>26983224</v>
+        <v>25813172</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1271,13 +1289,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="14">
-        <v>15.9084</v>
+        <v>16.1137</v>
       </c>
       <c r="C10" s="15">
-        <v>0.41</v>
+        <v>-0.63</v>
       </c>
       <c r="D10" s="16">
-        <v>27209514</v>
+        <v>25952809</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1287,13 +1305,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="14">
-        <v>15.8442</v>
+        <v>16.2156</v>
       </c>
       <c r="C11" s="15">
-        <v>0.02</v>
+        <v>0.82</v>
       </c>
       <c r="D11" s="16">
-        <v>27486255</v>
+        <v>25888965</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1303,13 +1321,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="14">
-        <v>15.8411</v>
+        <v>16.0833</v>
       </c>
       <c r="C12" s="15">
-        <v>-0.15</v>
+        <v>1.9</v>
       </c>
       <c r="D12" s="16">
-        <v>27540208</v>
+        <v>25898910</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1319,13 +1337,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="14">
-        <v>15.8651</v>
+        <v>15.7829</v>
       </c>
       <c r="C13" s="15">
-        <v>0.53</v>
+        <v>2.09</v>
       </c>
       <c r="D13" s="16">
-        <v>27732431</v>
+        <v>25547761</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1335,13 +1353,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="14">
-        <v>15.7809</v>
+        <v>15.4606</v>
       </c>
       <c r="C14" s="15">
-        <v>0.09</v>
+        <v>-4.14</v>
       </c>
       <c r="D14" s="16">
-        <v>27958865</v>
+        <v>25607229</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1351,13 +1369,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="14">
-        <v>15.7666</v>
+        <v>16.1277</v>
       </c>
       <c r="C15" s="15">
-        <v>-0.26</v>
+        <v>1.38</v>
       </c>
       <c r="D15" s="16">
-        <v>28144179</v>
+        <v>26983224</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1367,13 +1385,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="14">
-        <v>15.8083</v>
+        <v>15.9084</v>
       </c>
       <c r="C16" s="15">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="D16" s="16">
-        <v>28208442</v>
+        <v>27209514</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1383,13 +1401,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="14">
-        <v>15.7176</v>
+        <v>15.8442</v>
       </c>
       <c r="C17" s="15">
-        <v>-0.3</v>
+        <v>0.02</v>
       </c>
       <c r="D17" s="16">
-        <v>28147007</v>
+        <v>27486255</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1399,13 +1417,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="14">
-        <v>15.7645</v>
+        <v>15.8411</v>
       </c>
       <c r="C18" s="15">
-        <v>1.25</v>
+        <v>-0.15</v>
       </c>
       <c r="D18" s="16">
-        <v>27529765</v>
+        <v>27540208</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1415,13 +1433,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="14">
-        <v>15.5705</v>
+        <v>15.8651</v>
       </c>
       <c r="C19" s="15">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="D19" s="16">
-        <v>26537148</v>
+        <v>27732431</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1431,13 +1449,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="14">
-        <v>15.454</v>
+        <v>15.7809</v>
       </c>
       <c r="C20" s="15">
-        <v>-1.46</v>
+        <v>0.09</v>
       </c>
       <c r="D20" s="16">
-        <v>26410715</v>
+        <v>27958865</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1447,13 +1465,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="14">
-        <v>15.6831</v>
+        <v>15.7666</v>
       </c>
       <c r="C21" s="15">
-        <v>1.11</v>
+        <v>-0.26</v>
       </c>
       <c r="D21" s="16">
-        <v>26632265</v>
+        <v>28144179</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1463,13 +1481,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="14">
-        <v>15.5112</v>
+        <v>15.8083</v>
       </c>
       <c r="C22" s="15">
-        <v>1.67</v>
+        <v>0.58</v>
       </c>
       <c r="D22" s="16">
-        <v>26690099</v>
+        <v>28208442</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1479,13 +1497,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="14">
-        <v>15.2564</v>
+        <v>15.7176</v>
       </c>
       <c r="C23" s="15">
-        <v>0.09</v>
+        <v>-0.3</v>
       </c>
       <c r="D23" s="16">
-        <v>26845237</v>
+        <v>28147007</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1495,13 +1513,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="14">
-        <v>15.2426</v>
+        <v>15.7645</v>
       </c>
       <c r="C24" s="15">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="D24" s="16">
-        <v>26818264</v>
+        <v>27529765</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1511,13 +1529,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="14">
-        <v>15.135</v>
+        <v>15.5705</v>
       </c>
       <c r="C25" s="15">
-        <v>-1.04</v>
+        <v>0.75</v>
       </c>
       <c r="D25" s="16">
-        <v>26929428</v>
+        <v>26537148</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1527,13 +1545,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="14">
-        <v>15.2933</v>
+        <v>15.454</v>
       </c>
       <c r="C26" s="15">
-        <v>0.89</v>
+        <v>-1.46</v>
       </c>
       <c r="D26" s="16">
-        <v>27020006</v>
+        <v>26410715</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -1543,13 +1561,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="14">
-        <v>15.1584</v>
+        <v>15.6831</v>
       </c>
       <c r="C27" s="15">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="D27" s="16">
-        <v>27124319</v>
+        <v>26632265</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -1559,13 +1577,13 @@
         <v>33</v>
       </c>
       <c r="B28" s="14">
-        <v>15.0816</v>
+        <v>15.5112</v>
       </c>
       <c r="C28" s="15">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="D28" s="16">
-        <v>27294390</v>
+        <v>26690099</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -1575,13 +1593,13 @@
         <v>34</v>
       </c>
       <c r="B29" s="14">
-        <v>14.9271</v>
+        <v>15.2564</v>
       </c>
       <c r="C29" s="15">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="D29" s="16">
-        <v>27314404</v>
+        <v>26845237</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1591,13 +1609,13 @@
         <v>35</v>
       </c>
       <c r="B30" s="14">
-        <v>14.9928</v>
+        <v>15.2426</v>
       </c>
       <c r="C30" s="15">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="D30" s="16">
-        <v>26939895</v>
+        <v>26818264</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1607,13 +1625,13 @@
         <v>36</v>
       </c>
       <c r="B31" s="14">
-        <v>14.8465</v>
+        <v>15.135</v>
       </c>
       <c r="C31" s="15">
-        <v>-0.68</v>
+        <v>-1.04</v>
       </c>
       <c r="D31" s="16">
-        <v>25973217</v>
+        <v>26929428</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -1623,13 +1641,13 @@
         <v>37</v>
       </c>
       <c r="B32" s="14">
-        <v>14.9485</v>
+        <v>15.2933</v>
       </c>
       <c r="C32" s="15">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="D32" s="16">
-        <v>25671577</v>
+        <v>27020006</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
@@ -1639,13 +1657,13 @@
         <v>38</v>
       </c>
       <c r="B33" s="14">
-        <v>14.7835</v>
+        <v>15.1584</v>
       </c>
       <c r="C33" s="15">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="D33" s="16">
-        <v>25820021</v>
+        <v>27124319</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1655,13 +1673,13 @@
         <v>39</v>
       </c>
       <c r="B34" s="14">
-        <v>14.7222</v>
+        <v>15.0816</v>
       </c>
       <c r="C34" s="15">
-        <v>-0.1</v>
+        <v>1.04</v>
       </c>
       <c r="D34" s="16">
-        <v>26385972</v>
+        <v>27294390</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1671,13 +1689,13 @@
         <v>40</v>
       </c>
       <c r="B35" s="14">
-        <v>14.7365</v>
+        <v>14.9271</v>
       </c>
       <c r="C35" s="15">
-        <v>2.34</v>
+        <v>-0.44</v>
       </c>
       <c r="D35" s="16">
-        <v>26664397</v>
+        <v>27314404</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -1687,13 +1705,13 @@
         <v>41</v>
       </c>
       <c r="B36" s="14">
-        <v>14.4003</v>
+        <v>14.9928</v>
       </c>
       <c r="C36" s="15">
-        <v>3.26</v>
+        <v>0.99</v>
       </c>
       <c r="D36" s="16">
-        <v>26756224</v>
+        <v>26939895</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1703,13 +1721,13 @@
         <v>42</v>
       </c>
       <c r="B37" s="14">
-        <v>13.9463</v>
+        <v>14.8465</v>
       </c>
       <c r="C37" s="15">
-        <v>-0.49</v>
+        <v>-0.68</v>
       </c>
       <c r="D37" s="16">
-        <v>27100615</v>
+        <v>25973217</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -1719,13 +1737,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="14">
-        <v>14.0155</v>
+        <v>14.9485</v>
       </c>
       <c r="C38" s="15">
-        <v>-1.18</v>
+        <v>1.12</v>
       </c>
       <c r="D38" s="16">
-        <v>27434822</v>
+        <v>25671577</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -1735,13 +1753,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="14">
-        <v>14.1832</v>
+        <v>14.7835</v>
       </c>
       <c r="C39" s="15">
-        <v>-0.74</v>
+        <v>0.42</v>
       </c>
       <c r="D39" s="16">
-        <v>27612041</v>
+        <v>25820021</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -1751,13 +1769,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="14">
-        <v>14.2882</v>
+        <v>14.7222</v>
       </c>
       <c r="C40" s="15">
-        <v>1.03</v>
+        <v>-0.1</v>
       </c>
       <c r="D40" s="16">
-        <v>27609778</v>
+        <v>26385972</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -1767,13 +1785,13 @@
         <v>46</v>
       </c>
       <c r="B41" s="14">
-        <v>14.1431</v>
+        <v>14.7365</v>
       </c>
       <c r="C41" s="15">
-        <v>0.44</v>
+        <v>2.34</v>
       </c>
       <c r="D41" s="16">
-        <v>27618876</v>
+        <v>26664397</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -1783,13 +1801,13 @@
         <v>47</v>
       </c>
       <c r="B42" s="14">
-        <v>14.0815</v>
+        <v>14.4003</v>
       </c>
       <c r="C42" s="15">
-        <v>-0.43</v>
+        <v>3.26</v>
       </c>
       <c r="D42" s="16">
-        <v>27173910</v>
+        <v>26756224</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1799,13 +1817,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="14">
-        <v>14.1424</v>
+        <v>13.9463</v>
       </c>
       <c r="C43" s="15">
-        <v>0.89</v>
+        <v>-0.49</v>
       </c>
       <c r="D43" s="16">
-        <v>26373626</v>
+        <v>27100615</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -1815,13 +1833,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="14">
-        <v>14.0179</v>
+        <v>14.0155</v>
       </c>
       <c r="C44" s="15">
-        <v>1.09</v>
+        <v>-1.18</v>
       </c>
       <c r="D44" s="16">
-        <v>26516596</v>
+        <v>27434822</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -1831,13 +1849,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="14">
-        <v>13.8662</v>
+        <v>14.1832</v>
       </c>
       <c r="C45" s="15">
-        <v>-0.46</v>
+        <v>-0.74</v>
       </c>
       <c r="D45" s="16">
-        <v>26953299</v>
+        <v>27612041</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -1847,13 +1865,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="14">
-        <v>13.9307</v>
+        <v>14.2882</v>
       </c>
       <c r="C46" s="15">
-        <v>2.95</v>
+        <v>1.03</v>
       </c>
       <c r="D46" s="16">
-        <v>27138500</v>
+        <v>27609778</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -1863,13 +1881,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="14">
-        <v>13.532</v>
+        <v>14.1431</v>
       </c>
       <c r="C47" s="15">
-        <v>-1.87</v>
+        <v>0.44</v>
       </c>
       <c r="D47" s="16">
-        <v>27375019</v>
+        <v>27618876</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -1879,13 +1897,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="14">
-        <v>13.7904</v>
+        <v>14.0815</v>
       </c>
       <c r="C48" s="15">
-        <v>2.68</v>
+        <v>-0.43</v>
       </c>
       <c r="D48" s="16">
-        <v>27611383</v>
+        <v>27173910</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -1895,13 +1913,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="14">
-        <v>13.4301</v>
+        <v>14.1424</v>
       </c>
       <c r="C49" s="15">
-        <v>1.4</v>
+        <v>0.89</v>
       </c>
       <c r="D49" s="16">
-        <v>27712668</v>
+        <v>26373626</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -1911,13 +1929,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="14">
-        <v>13.2445</v>
+        <v>14.0179</v>
       </c>
       <c r="C50" s="15">
-        <v>-2.9</v>
+        <v>1.09</v>
       </c>
       <c r="D50" s="16">
-        <v>28141058</v>
+        <v>26516596</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -1927,13 +1945,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="14">
-        <v>13.6393</v>
+        <v>13.8662</v>
       </c>
       <c r="C51" s="15">
-        <v>-3.67</v>
+        <v>-0.46</v>
       </c>
       <c r="D51" s="16">
-        <v>28579838</v>
+        <v>26953299</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -1943,13 +1961,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="14">
-        <v>14.1582</v>
+        <v>13.9307</v>
       </c>
       <c r="C52" s="15">
-        <v>3.68</v>
+        <v>2.95</v>
       </c>
       <c r="D52" s="16">
-        <v>28682522</v>
+        <v>27138500</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -1959,13 +1977,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="14">
-        <v>13.6559</v>
+        <v>13.532</v>
       </c>
       <c r="C53" s="15">
-        <v>-3.26</v>
+        <v>-1.87</v>
       </c>
       <c r="D53" s="16">
-        <v>28723130</v>
+        <v>27375019</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1975,13 +1993,13 @@
         <v>59</v>
       </c>
       <c r="B54" s="14">
-        <v>14.1159</v>
+        <v>13.7904</v>
       </c>
       <c r="C54" s="15">
-        <v>-0.84</v>
+        <v>2.68</v>
       </c>
       <c r="D54" s="16">
-        <v>28480323</v>
+        <v>27611383</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -1991,13 +2009,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="14">
-        <v>14.2348</v>
+        <v>13.4301</v>
       </c>
       <c r="C55" s="15">
-        <v>-1.95</v>
+        <v>1.4</v>
       </c>
       <c r="D55" s="16">
-        <v>27391640</v>
+        <v>27712668</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -2007,13 +2025,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="14">
-        <v>14.5183</v>
+        <v>13.2445</v>
       </c>
       <c r="C56" s="15">
-        <v>-1.06</v>
+        <v>-2.9</v>
       </c>
       <c r="D56" s="16">
-        <v>27176414</v>
+        <v>28141058</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -2023,13 +2041,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="14">
-        <v>14.6738</v>
+        <v>13.6393</v>
       </c>
       <c r="C57" s="15">
-        <v>-2.4</v>
+        <v>-3.67</v>
       </c>
       <c r="D57" s="16">
-        <v>27648035</v>
+        <v>28579838</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -2039,13 +2057,13 @@
         <v>63</v>
       </c>
       <c r="B58" s="14">
-        <v>15.0341</v>
+        <v>14.1582</v>
       </c>
       <c r="C58" s="15">
-        <v>-2.18</v>
+        <v>3.68</v>
       </c>
       <c r="D58" s="16">
-        <v>27793878</v>
+        <v>28682522</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -2055,13 +2073,13 @@
         <v>64</v>
       </c>
       <c r="B59" s="14">
-        <v>15.3697</v>
+        <v>13.6559</v>
       </c>
       <c r="C59" s="15">
-        <v>1.06</v>
+        <v>-3.26</v>
       </c>
       <c r="D59" s="16">
-        <v>27629335</v>
+        <v>28723130</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -2071,13 +2089,13 @@
         <v>65</v>
       </c>
       <c r="B60" s="14">
-        <v>15.2091</v>
+        <v>14.1159</v>
       </c>
       <c r="C60" s="15">
-        <v>-0.29</v>
+        <v>-0.84</v>
       </c>
       <c r="D60" s="16">
-        <v>27204612</v>
+        <v>28480323</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -2087,13 +2105,13 @@
         <v>66</v>
       </c>
       <c r="B61" s="14">
-        <v>15.2538</v>
+        <v>14.2348</v>
       </c>
       <c r="C61" s="15">
-        <v>0.73</v>
+        <v>-1.95</v>
       </c>
       <c r="D61" s="16">
-        <v>27113066</v>
+        <v>27391640</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -2103,13 +2121,13 @@
         <v>67</v>
       </c>
       <c r="B62" s="14">
-        <v>15.144</v>
+        <v>14.5183</v>
       </c>
       <c r="C62" s="15">
-        <v>-1.28</v>
+        <v>-1.06</v>
       </c>
       <c r="D62" s="16">
-        <v>27182928</v>
+        <v>27176414</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -2119,13 +2137,13 @@
         <v>68</v>
       </c>
       <c r="B63" s="14">
-        <v>15.3402</v>
+        <v>14.6738</v>
       </c>
       <c r="C63" s="15">
-        <v>0.52</v>
+        <v>-2.4</v>
       </c>
       <c r="D63" s="16">
-        <v>27428081</v>
+        <v>27648035</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -2135,13 +2153,13 @@
         <v>69</v>
       </c>
       <c r="B64" s="14">
-        <v>15.2612</v>
+        <v>15.0341</v>
       </c>
       <c r="C64" s="15">
-        <v>0.79</v>
+        <v>-2.18</v>
       </c>
       <c r="D64" s="16">
-        <v>27409830</v>
+        <v>27793878</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -2151,13 +2169,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="14">
-        <v>15.1419</v>
+        <v>15.3697</v>
       </c>
       <c r="C65" s="15">
-        <v>0.41</v>
+        <v>1.06</v>
       </c>
       <c r="D65" s="16">
-        <v>27240164</v>
+        <v>27629335</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -2167,13 +2185,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="14">
-        <v>15.0805</v>
+        <v>15.2091</v>
       </c>
       <c r="C66" s="15">
-        <v>0.49</v>
+        <v>-0.29</v>
       </c>
       <c r="D66" s="16">
-        <v>26175558</v>
+        <v>27204612</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -2183,13 +2201,13 @@
         <v>72</v>
       </c>
       <c r="B67" s="14">
-        <v>15.0077</v>
+        <v>15.2538</v>
       </c>
       <c r="C67" s="15">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="D67" s="16">
-        <v>24579635</v>
+        <v>27113066</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -2199,13 +2217,13 @@
         <v>73</v>
       </c>
       <c r="B68" s="14">
-        <v>14.9567</v>
+        <v>15.144</v>
       </c>
       <c r="C68" s="15">
-        <v>1.57</v>
+        <v>-1.28</v>
       </c>
       <c r="D68" s="16">
-        <v>23850708</v>
+        <v>27182928</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -2215,13 +2233,13 @@
         <v>74</v>
       </c>
       <c r="B69" s="14">
-        <v>14.7259</v>
+        <v>15.3402</v>
       </c>
       <c r="C69" s="15">
-        <v>0.18</v>
+        <v>0.52</v>
       </c>
       <c r="D69" s="16">
-        <v>23635941</v>
+        <v>27428081</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -2231,13 +2249,13 @@
         <v>75</v>
       </c>
       <c r="B70" s="14">
-        <v>14.6994</v>
+        <v>15.2612</v>
       </c>
       <c r="C70" s="15">
-        <v>-0.47</v>
+        <v>0.79</v>
       </c>
       <c r="D70" s="16">
-        <v>23438140</v>
+        <v>27409830</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -2247,13 +2265,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="14">
-        <v>14.7691</v>
+        <v>15.1419</v>
       </c>
       <c r="C71" s="15">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="D71" s="16">
-        <v>23337460</v>
+        <v>27240164</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -2263,13 +2281,13 @@
         <v>77</v>
       </c>
       <c r="B72" s="14">
-        <v>14.7203</v>
+        <v>15.0805</v>
       </c>
       <c r="C72" s="15">
-        <v>3.01</v>
+        <v>0.49</v>
       </c>
       <c r="D72" s="16">
-        <v>22878949</v>
+        <v>26175558</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -2279,13 +2297,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="14">
-        <v>14.2904</v>
+        <v>15.0077</v>
       </c>
       <c r="C73" s="15">
-        <v>-1.11</v>
+        <v>0.34</v>
       </c>
       <c r="D73" s="16">
-        <v>22682017</v>
+        <v>24579635</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
@@ -2295,13 +2313,13 @@
         <v>79</v>
       </c>
       <c r="B74" s="14">
-        <v>14.4513</v>
+        <v>14.9567</v>
       </c>
       <c r="C74" s="15">
-        <v>-0.24</v>
+        <v>1.57</v>
       </c>
       <c r="D74" s="16">
-        <v>22456814</v>
+        <v>23850708</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
@@ -2311,13 +2329,13 @@
         <v>80</v>
       </c>
       <c r="B75" s="14">
-        <v>14.4862</v>
+        <v>14.7259</v>
       </c>
       <c r="C75" s="15">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="D75" s="16">
-        <v>22273337</v>
+        <v>23635941</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
@@ -2327,13 +2345,13 @@
         <v>81</v>
       </c>
       <c r="B76" s="14">
-        <v>14.4221</v>
+        <v>14.6994</v>
       </c>
       <c r="C76" s="15">
-        <v>0.08</v>
+        <v>-0.47</v>
       </c>
       <c r="D76" s="16">
-        <v>22059075</v>
+        <v>23438140</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
@@ -2343,13 +2361,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="14">
-        <v>14.41</v>
+        <v>14.7691</v>
       </c>
       <c r="C77" s="15">
-        <v>1.55</v>
+        <v>0.33</v>
       </c>
       <c r="D77" s="16">
-        <v>21534754</v>
+        <v>23337460</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
@@ -2359,13 +2377,13 @@
         <v>83</v>
       </c>
       <c r="B78" s="14">
-        <v>14.1899</v>
+        <v>14.7203</v>
       </c>
       <c r="C78" s="15">
-        <v>0.96</v>
+        <v>3.01</v>
       </c>
       <c r="D78" s="16">
-        <v>20601299</v>
+        <v>22878949</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -2375,13 +2393,13 @@
         <v>84</v>
       </c>
       <c r="B79" s="14">
-        <v>14.0544</v>
+        <v>14.2904</v>
       </c>
       <c r="C79" s="15">
-        <v>1.71</v>
+        <v>-1.11</v>
       </c>
       <c r="D79" s="16">
-        <v>20180084</v>
+        <v>22682017</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
@@ -2391,13 +2409,13 @@
         <v>85</v>
       </c>
       <c r="B80" s="14">
-        <v>13.8179</v>
+        <v>14.4513</v>
       </c>
       <c r="C80" s="15">
-        <v>-2.09</v>
+        <v>-0.24</v>
       </c>
       <c r="D80" s="16">
-        <v>20063482</v>
+        <v>22456814</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
@@ -2407,13 +2425,13 @@
         <v>86</v>
       </c>
       <c r="B81" s="14">
-        <v>14.1131</v>
+        <v>14.4862</v>
       </c>
       <c r="C81" s="15">
-        <v>-1.24</v>
+        <v>0.44</v>
       </c>
       <c r="D81" s="16">
-        <v>20604649</v>
+        <v>22273337</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2423,13 +2441,13 @@
         <v>87</v>
       </c>
       <c r="B82" s="14">
-        <v>14.2903</v>
+        <v>14.4221</v>
       </c>
       <c r="C82" s="15">
-        <v>-0.16</v>
+        <v>0.08</v>
       </c>
       <c r="D82" s="16">
-        <v>20591533</v>
+        <v>22059075</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
@@ -2439,13 +2457,13 @@
         <v>88</v>
       </c>
       <c r="B83" s="14">
-        <v>14.3138</v>
+        <v>14.41</v>
       </c>
       <c r="C83" s="15">
-        <v>-0.03</v>
+        <v>1.55</v>
       </c>
       <c r="D83" s="16">
-        <v>20416510</v>
+        <v>21534754</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
@@ -2455,13 +2473,13 @@
         <v>89</v>
       </c>
       <c r="B84" s="14">
-        <v>14.3184</v>
+        <v>14.1899</v>
       </c>
       <c r="C84" s="15">
-        <v>0.34</v>
+        <v>0.96</v>
       </c>
       <c r="D84" s="16">
-        <v>20375465</v>
+        <v>20601299</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
@@ -2471,13 +2489,13 @@
         <v>90</v>
       </c>
       <c r="B85" s="14">
-        <v>14.2694</v>
+        <v>14.0544</v>
       </c>
       <c r="C85" s="15">
-        <v>0.02</v>
+        <v>1.71</v>
       </c>
       <c r="D85" s="16">
-        <v>20292025</v>
+        <v>20180084</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
@@ -2487,13 +2505,13 @@
         <v>91</v>
       </c>
       <c r="B86" s="14">
-        <v>14.266</v>
+        <v>13.8179</v>
       </c>
       <c r="C86" s="15">
-        <v>0.23</v>
+        <v>-2.09</v>
       </c>
       <c r="D86" s="16">
-        <v>20329763</v>
+        <v>20063482</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
@@ -2503,13 +2521,13 @@
         <v>92</v>
       </c>
       <c r="B87" s="14">
-        <v>14.2337</v>
+        <v>14.1131</v>
       </c>
       <c r="C87" s="15">
-        <v>-0.17</v>
+        <v>-1.24</v>
       </c>
       <c r="D87" s="16">
-        <v>20319771</v>
+        <v>20604649</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2519,13 +2537,13 @@
         <v>93</v>
       </c>
       <c r="B88" s="14">
-        <v>14.2572</v>
+        <v>14.2903</v>
       </c>
       <c r="C88" s="15">
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="D88" s="16">
-        <v>20372415</v>
+        <v>20591533</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
@@ -2535,13 +2553,13 @@
         <v>94</v>
       </c>
       <c r="B89" s="14">
-        <v>14.2319</v>
+        <v>14.3138</v>
       </c>
       <c r="C89" s="15">
-        <v>1.18</v>
+        <v>-0.03</v>
       </c>
       <c r="D89" s="16">
-        <v>20322696</v>
+        <v>20416510</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -2551,13 +2569,13 @@
         <v>95</v>
       </c>
       <c r="B90" s="14">
-        <v>14.0663</v>
+        <v>14.3184</v>
       </c>
       <c r="C90" s="15">
-        <v>-0.54</v>
+        <v>0.34</v>
       </c>
       <c r="D90" s="16">
-        <v>19749412</v>
+        <v>20375465</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -2567,13 +2585,13 @@
         <v>96</v>
       </c>
       <c r="B91" s="14">
-        <v>14.1427</v>
+        <v>14.2694</v>
       </c>
       <c r="C91" s="15">
-        <v>0.86</v>
+        <v>0.02</v>
       </c>
       <c r="D91" s="16">
-        <v>18764505</v>
+        <v>20292025</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -2583,13 +2601,13 @@
         <v>97</v>
       </c>
       <c r="B92" s="14">
-        <v>14.022</v>
+        <v>14.266</v>
       </c>
       <c r="C92" s="15">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="D92" s="16">
-        <v>18271214</v>
+        <v>20329763</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -2599,13 +2617,13 @@
         <v>98</v>
       </c>
       <c r="B93" s="14">
-        <v>13.9466</v>
+        <v>14.2337</v>
       </c>
       <c r="C93" s="15">
-        <v>0.65</v>
+        <v>-0.17</v>
       </c>
       <c r="D93" s="16">
-        <v>18210255</v>
+        <v>20319771</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -2615,13 +2633,13 @@
         <v>99</v>
       </c>
       <c r="B94" s="14">
-        <v>13.8567</v>
+        <v>14.2572</v>
       </c>
       <c r="C94" s="15">
-        <v>0.8</v>
+        <v>0.18</v>
       </c>
       <c r="D94" s="16">
-        <v>18236514</v>
+        <v>20372415</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
@@ -2631,13 +2649,13 @@
         <v>100</v>
       </c>
       <c r="B95" s="14">
-        <v>13.7473</v>
+        <v>14.2319</v>
       </c>
       <c r="C95" s="15">
-        <v>-0.59</v>
+        <v>1.18</v>
       </c>
       <c r="D95" s="16">
-        <v>18303967</v>
+        <v>20322696</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
@@ -2647,13 +2665,13 @@
         <v>101</v>
       </c>
       <c r="B96" s="14">
-        <v>13.8294</v>
+        <v>14.0663</v>
       </c>
       <c r="C96" s="15">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="D96" s="16">
-        <v>18441258</v>
+        <v>19749412</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
@@ -2663,13 +2681,13 @@
         <v>102</v>
       </c>
       <c r="B97" s="14">
-        <v>13.8377</v>
+        <v>14.1427</v>
       </c>
       <c r="C97" s="15">
-        <v>-1</v>
+        <v>0.86</v>
       </c>
       <c r="D97" s="16">
-        <v>18545907</v>
+        <v>18764505</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -2679,13 +2697,13 @@
         <v>103</v>
       </c>
       <c r="B98" s="14">
-        <v>13.9769</v>
+        <v>14.022</v>
       </c>
       <c r="C98" s="15">
-        <v>0.07</v>
+        <v>0.54</v>
       </c>
       <c r="D98" s="16">
-        <v>18671095</v>
+        <v>18271214</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -2695,13 +2713,13 @@
         <v>104</v>
       </c>
       <c r="B99" s="14">
-        <v>13.9674</v>
+        <v>13.9466</v>
       </c>
       <c r="C99" s="15">
-        <v>-0.54</v>
+        <v>0.65</v>
       </c>
       <c r="D99" s="16">
-        <v>18776963</v>
+        <v>18210255</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -2711,13 +2729,13 @@
         <v>105</v>
       </c>
       <c r="B100" s="14">
-        <v>14.0435</v>
+        <v>13.8567</v>
       </c>
       <c r="C100" s="15">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="D100" s="16">
-        <v>18835597</v>
+        <v>18236514</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -2727,13 +2745,13 @@
         <v>106</v>
       </c>
       <c r="B101" s="14">
-        <v>13.9962</v>
+        <v>13.7473</v>
       </c>
       <c r="C101" s="15">
-        <v>0.03</v>
+        <v>-0.59</v>
       </c>
       <c r="D101" s="16">
-        <v>18875257</v>
+        <v>18303967</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
@@ -2743,13 +2761,13 @@
         <v>107</v>
       </c>
       <c r="B102" s="14">
-        <v>13.9922</v>
+        <v>13.8294</v>
       </c>
       <c r="C102" s="15">
-        <v>-0.66</v>
+        <v>-0.06</v>
       </c>
       <c r="D102" s="16">
-        <v>18825827</v>
+        <v>18441258</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
@@ -2759,13 +2777,13 @@
         <v>108</v>
       </c>
       <c r="B103" s="14">
-        <v>14.0845</v>
+        <v>13.8377</v>
       </c>
       <c r="C103" s="15">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
       <c r="D103" s="16">
-        <v>18364121</v>
+        <v>18545907</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -2775,13 +2793,13 @@
         <v>109</v>
       </c>
       <c r="B104" s="14">
-        <v>13.9586</v>
+        <v>13.9769</v>
       </c>
       <c r="C104" s="15">
-        <v>-0.15</v>
+        <v>0.07</v>
       </c>
       <c r="D104" s="16">
-        <v>18284776</v>
+        <v>18671095</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
@@ -2791,13 +2809,13 @@
         <v>110</v>
       </c>
       <c r="B105" s="14">
-        <v>13.9788</v>
+        <v>13.9674</v>
       </c>
       <c r="C105" s="15">
-        <v>-0.76</v>
+        <v>-0.54</v>
       </c>
       <c r="D105" s="16">
-        <v>18342371</v>
+        <v>18776963</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -2807,13 +2825,13 @@
         <v>111</v>
       </c>
       <c r="B106" s="14">
-        <v>14.0863</v>
+        <v>14.0435</v>
       </c>
       <c r="C106" s="15">
-        <v>0.07</v>
+        <v>0.34</v>
       </c>
       <c r="D106" s="16">
-        <v>18424532</v>
+        <v>18835597</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
@@ -2823,13 +2841,13 @@
         <v>112</v>
       </c>
       <c r="B107" s="14">
-        <v>14.0764</v>
+        <v>13.9962</v>
       </c>
       <c r="C107" s="15">
-        <v>-0.33</v>
+        <v>0.03</v>
       </c>
       <c r="D107" s="16">
-        <v>18445080</v>
+        <v>18875257</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
@@ -2839,13 +2857,13 @@
         <v>113</v>
       </c>
       <c r="B108" s="14">
-        <v>14.1224</v>
+        <v>13.9922</v>
       </c>
       <c r="C108" s="15">
-        <v>-0.42</v>
+        <v>-0.66</v>
       </c>
       <c r="D108" s="16">
-        <v>17813846</v>
+        <v>18825827</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
@@ -2855,13 +2873,13 @@
         <v>114</v>
       </c>
       <c r="B109" s="14">
-        <v>14.1822</v>
+        <v>14.0845</v>
       </c>
       <c r="C109" s="15">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="D109" s="16">
-        <v>17855054</v>
+        <v>18364121</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
@@ -2871,13 +2889,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="14">
-        <v>14.095</v>
+        <v>13.9586</v>
       </c>
       <c r="C110" s="15">
-        <v>0.61</v>
+        <v>-0.15</v>
       </c>
       <c r="D110" s="16">
-        <v>17944906</v>
+        <v>18284776</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
@@ -2887,13 +2905,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="14">
-        <v>14.0101</v>
+        <v>13.9788</v>
       </c>
       <c r="C111" s="15">
-        <v>0.1</v>
+        <v>-0.76</v>
       </c>
       <c r="D111" s="16">
-        <v>18048746</v>
+        <v>18342371</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
@@ -2903,13 +2921,13 @@
         <v>117</v>
       </c>
       <c r="B112" s="14">
-        <v>13.9959</v>
+        <v>14.0863</v>
       </c>
       <c r="C112" s="15">
-        <v>-0.01</v>
+        <v>0.07</v>
       </c>
       <c r="D112" s="16">
-        <v>18112954</v>
+        <v>18424532</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
@@ -2919,13 +2937,13 @@
         <v>118</v>
       </c>
       <c r="B113" s="14">
-        <v>13.997</v>
+        <v>14.0764</v>
       </c>
       <c r="C113" s="15">
-        <v>-0.63</v>
+        <v>-0.33</v>
       </c>
       <c r="D113" s="16">
-        <v>18156436</v>
+        <v>18445080</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
@@ -2935,13 +2953,13 @@
         <v>119</v>
       </c>
       <c r="B114" s="14">
-        <v>14.0851</v>
+        <v>14.1224</v>
       </c>
       <c r="C114" s="15">
-        <v>0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="D114" s="16">
-        <v>17758697</v>
+        <v>17813846</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
@@ -2951,13 +2969,13 @@
         <v>120</v>
       </c>
       <c r="B115" s="14">
-        <v>14.0615</v>
+        <v>14.1822</v>
       </c>
       <c r="C115" s="15">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="D115" s="16">
-        <v>17190410</v>
+        <v>17855054</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -2967,13 +2985,13 @@
         <v>121</v>
       </c>
       <c r="B116" s="14">
-        <v>13.9985</v>
+        <v>14.095</v>
       </c>
       <c r="C116" s="15">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="D116" s="16">
-        <v>16952800</v>
+        <v>17944906</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
@@ -2983,13 +3001,13 @@
         <v>122</v>
       </c>
       <c r="B117" s="14">
-        <v>13.9472</v>
+        <v>14.0101</v>
       </c>
       <c r="C117" s="15">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="D117" s="16">
-        <v>16984701</v>
+        <v>18048746</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
@@ -2999,13 +3017,13 @@
         <v>123</v>
       </c>
       <c r="B118" s="14">
-        <v>13.8937</v>
+        <v>13.9959</v>
       </c>
       <c r="C118" s="15">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="D118" s="16">
-        <v>17011954</v>
+        <v>18112954</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
@@ -3015,13 +3033,13 @@
         <v>124</v>
       </c>
       <c r="B119" s="14">
-        <v>13.9847</v>
+        <v>13.997</v>
       </c>
       <c r="C119" s="15">
-        <v>0.95</v>
+        <v>-0.63</v>
       </c>
       <c r="D119" s="16">
-        <v>17035674</v>
+        <v>18156436</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
@@ -3031,13 +3049,13 @@
         <v>125</v>
       </c>
       <c r="B120" s="14">
-        <v>13.8534</v>
+        <v>14.0851</v>
       </c>
       <c r="C120" s="15">
-        <v>-0.34</v>
+        <v>0.17</v>
       </c>
       <c r="D120" s="16">
-        <v>16555499</v>
+        <v>17758697</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
@@ -3047,13 +3065,13 @@
         <v>126</v>
       </c>
       <c r="B121" s="14">
-        <v>13.8999</v>
+        <v>14.0615</v>
       </c>
       <c r="C121" s="15">
-        <v>-0.27</v>
+        <v>0.45</v>
       </c>
       <c r="D121" s="16">
-        <v>16564445</v>
+        <v>17190410</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
@@ -3063,13 +3081,13 @@
         <v>127</v>
       </c>
       <c r="B122" s="14">
-        <v>13.9379</v>
+        <v>13.9985</v>
       </c>
       <c r="C122" s="15">
-        <v>0.07</v>
+        <v>0.37</v>
       </c>
       <c r="D122" s="16">
-        <v>16601729</v>
+        <v>16952800</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
@@ -3079,13 +3097,13 @@
         <v>128</v>
       </c>
       <c r="B123" s="14">
-        <v>13.9288</v>
+        <v>13.9472</v>
       </c>
       <c r="C123" s="15">
-        <v>-0.02</v>
+        <v>0.39</v>
       </c>
       <c r="D123" s="16">
-        <v>16602821</v>
+        <v>16984701</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -3095,13 +3113,13 @@
         <v>129</v>
       </c>
       <c r="B124" s="14">
-        <v>13.9309</v>
+        <v>13.8937</v>
       </c>
       <c r="C124" s="15">
-        <v>0.38</v>
+        <v>-0.65</v>
       </c>
       <c r="D124" s="16">
-        <v>16604572</v>
+        <v>17011954</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
@@ -3111,13 +3129,13 @@
         <v>130</v>
       </c>
       <c r="B125" s="14">
-        <v>13.8785</v>
+        <v>13.9847</v>
       </c>
       <c r="C125" s="15">
-        <v>-0.14</v>
+        <v>0.95</v>
       </c>
       <c r="D125" s="16">
-        <v>16580643</v>
+        <v>17035674</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -3127,13 +3145,13 @@
         <v>131</v>
       </c>
       <c r="B126" s="14">
-        <v>13.8972</v>
+        <v>13.8534</v>
       </c>
       <c r="C126" s="15">
-        <v>0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="D126" s="16">
-        <v>16067893</v>
+        <v>16555499</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
@@ -3143,13 +3161,13 @@
         <v>132</v>
       </c>
       <c r="B127" s="14">
-        <v>13.8471</v>
+        <v>13.8999</v>
       </c>
       <c r="C127" s="15">
-        <v>0.11</v>
+        <v>-0.27</v>
       </c>
       <c r="D127" s="16">
-        <v>15348175</v>
+        <v>16564445</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
@@ -3159,13 +3177,13 @@
         <v>133</v>
       </c>
       <c r="B128" s="14">
-        <v>13.8326</v>
+        <v>13.9379</v>
       </c>
       <c r="C128" s="15">
         <v>0.07</v>
       </c>
       <c r="D128" s="16">
-        <v>15107843</v>
+        <v>16601729</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
@@ -3175,13 +3193,13 @@
         <v>134</v>
       </c>
       <c r="B129" s="14">
-        <v>13.8236</v>
+        <v>13.9288</v>
       </c>
       <c r="C129" s="15">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="D129" s="16">
-        <v>14970972</v>
+        <v>16602821</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
@@ -3191,13 +3209,13 @@
         <v>135</v>
       </c>
       <c r="B130" s="14">
-        <v>13.8241</v>
+        <v>13.9309</v>
       </c>
       <c r="C130" s="15">
-        <v>-0.28</v>
+        <v>0.38</v>
       </c>
       <c r="D130" s="16">
-        <v>15045700</v>
+        <v>16604572</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
@@ -3207,13 +3225,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="14">
-        <v>13.8632</v>
+        <v>13.8785</v>
       </c>
       <c r="C131" s="15">
-        <v>-1.08</v>
+        <v>-0.14</v>
       </c>
       <c r="D131" s="16">
-        <v>15031857</v>
+        <v>16580643</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
@@ -3223,13 +3241,13 @@
         <v>137</v>
       </c>
       <c r="B132" s="14">
-        <v>14.014</v>
+        <v>13.8972</v>
       </c>
       <c r="C132" s="15">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="D132" s="16">
-        <v>14669668</v>
+        <v>16067893</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
@@ -3239,13 +3257,13 @@
         <v>138</v>
       </c>
       <c r="B133" s="14">
-        <v>13.9557</v>
+        <v>13.8471</v>
       </c>
       <c r="C133" s="15">
-        <v>1.17</v>
+        <v>0.11</v>
       </c>
       <c r="D133" s="16">
-        <v>14653804</v>
+        <v>15348175</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
@@ -3255,13 +3273,13 @@
         <v>139</v>
       </c>
       <c r="B134" s="14">
-        <v>13.7949</v>
+        <v>13.8326</v>
       </c>
       <c r="C134" s="15">
-        <v>-0.28</v>
+        <v>0.07</v>
       </c>
       <c r="D134" s="16">
-        <v>14652445</v>
+        <v>15107843</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
@@ -3271,13 +3289,13 @@
         <v>140</v>
       </c>
       <c r="B135" s="14">
-        <v>13.8331</v>
+        <v>13.8236</v>
       </c>
       <c r="C135" s="15">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="D135" s="16">
-        <v>14639361</v>
+        <v>14970972</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
@@ -3287,13 +3305,13 @@
         <v>141</v>
       </c>
       <c r="B136" s="14">
-        <v>13.9982</v>
+        <v>13.8241</v>
       </c>
       <c r="C136" s="15">
-        <v>1.11</v>
+        <v>-0.28</v>
       </c>
       <c r="D136" s="16">
-        <v>14636809</v>
+        <v>15045700</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
@@ -3303,13 +3321,13 @@
         <v>142</v>
       </c>
       <c r="B137" s="14">
-        <v>13.845</v>
+        <v>13.8632</v>
       </c>
       <c r="C137" s="15">
-        <v>-1.07</v>
+        <v>-1.08</v>
       </c>
       <c r="D137" s="16">
-        <v>14433805</v>
+        <v>15031857</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
@@ -3319,13 +3337,13 @@
         <v>143</v>
       </c>
       <c r="B138" s="14">
-        <v>13.9953</v>
+        <v>14.014</v>
       </c>
       <c r="C138" s="15">
-        <v>-0.27</v>
+        <v>0.42</v>
       </c>
       <c r="D138" s="16">
-        <v>13989441</v>
+        <v>14669668</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
@@ -3335,13 +3353,13 @@
         <v>144</v>
       </c>
       <c r="B139" s="14">
-        <v>14.0336</v>
+        <v>13.9557</v>
       </c>
       <c r="C139" s="15">
-        <v>-0.38</v>
+        <v>1.17</v>
       </c>
       <c r="D139" s="16">
-        <v>13566681</v>
+        <v>14653804</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
@@ -3351,13 +3369,13 @@
         <v>145</v>
       </c>
       <c r="B140" s="14">
-        <v>14.087</v>
+        <v>13.7949</v>
       </c>
       <c r="C140" s="15">
-        <v>0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="D140" s="16">
-        <v>13137192</v>
+        <v>14652445</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
@@ -3367,13 +3385,13 @@
         <v>146</v>
       </c>
       <c r="B141" s="14">
-        <v>14.0394</v>
+        <v>13.8331</v>
       </c>
       <c r="C141" s="15">
-        <v>1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="D141" s="16">
-        <v>12985801</v>
+        <v>14639361</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
@@ -3383,13 +3401,13 @@
         <v>147</v>
       </c>
       <c r="B142" s="14">
-        <v>13.8773</v>
+        <v>13.9982</v>
       </c>
       <c r="C142" s="15">
-        <v>0.97</v>
+        <v>1.11</v>
       </c>
       <c r="D142" s="16">
-        <v>12941290</v>
+        <v>14636809</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
@@ -3399,13 +3417,13 @@
         <v>148</v>
       </c>
       <c r="B143" s="14">
-        <v>13.7443</v>
+        <v>13.845</v>
       </c>
       <c r="C143" s="15">
-        <v>0.04</v>
+        <v>-1.07</v>
       </c>
       <c r="D143" s="16">
-        <v>12972634</v>
+        <v>14433805</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
@@ -3415,13 +3433,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="14">
-        <v>13.7392</v>
+        <v>13.9953</v>
       </c>
       <c r="C144" s="15">
-        <v>0.73</v>
+        <v>-0.27</v>
       </c>
       <c r="D144" s="16">
-        <v>12694568</v>
+        <v>13989441</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
@@ -3431,13 +3449,13 @@
         <v>150</v>
       </c>
       <c r="B145" s="14">
-        <v>13.6402</v>
+        <v>14.0336</v>
       </c>
       <c r="C145" s="15">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="D145" s="16">
-        <v>12659561</v>
+        <v>13566681</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
@@ -3447,13 +3465,13 @@
         <v>151</v>
       </c>
       <c r="B146" s="14">
-        <v>13.678</v>
+        <v>14.087</v>
       </c>
       <c r="C146" s="15">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="D146" s="16">
-        <v>12821290</v>
+        <v>13137192</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
@@ -3463,13 +3481,13 @@
         <v>152</v>
       </c>
       <c r="B147" s="14">
-        <v>13.6484</v>
+        <v>14.0394</v>
       </c>
       <c r="C147" s="15">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="D147" s="16">
-        <v>12815298</v>
+        <v>12985801</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
@@ -3479,13 +3497,13 @@
         <v>153</v>
       </c>
       <c r="B148" s="14">
-        <v>13.5523</v>
+        <v>13.8773</v>
       </c>
       <c r="C148" s="15">
-        <v>-0.16</v>
+        <v>0.97</v>
       </c>
       <c r="D148" s="16">
-        <v>12778173</v>
+        <v>12941290</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
@@ -3495,13 +3513,13 @@
         <v>154</v>
       </c>
       <c r="B149" s="14">
-        <v>13.5734</v>
+        <v>13.7443</v>
       </c>
       <c r="C149" s="15">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="D149" s="16">
-        <v>12525374</v>
+        <v>12972634</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
@@ -3511,13 +3529,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="14">
-        <v>13.5259</v>
+        <v>13.7392</v>
       </c>
       <c r="C150" s="15">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="D150" s="16">
-        <v>12222638</v>
+        <v>12694568</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
@@ -3527,13 +3545,13 @@
         <v>156</v>
       </c>
       <c r="B151" s="14">
-        <v>13.4447</v>
+        <v>13.6402</v>
       </c>
       <c r="C151" s="15">
-        <v>0.33</v>
+        <v>-0.28</v>
       </c>
       <c r="D151" s="16">
-        <v>11902533</v>
+        <v>12659561</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
@@ -3543,13 +3561,13 @@
         <v>157</v>
       </c>
       <c r="B152" s="14">
-        <v>13.4005</v>
+        <v>13.678</v>
       </c>
       <c r="C152" s="15">
         <v>0.22</v>
       </c>
       <c r="D152" s="16">
-        <v>11564711</v>
+        <v>12821290</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
@@ -3559,13 +3577,13 @@
         <v>158</v>
       </c>
       <c r="B153" s="14">
-        <v>13.3707</v>
+        <v>13.6484</v>
       </c>
       <c r="C153" s="15">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="D153" s="16">
-        <v>11491616</v>
+        <v>12815298</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
@@ -3575,13 +3593,13 @@
         <v>159</v>
       </c>
       <c r="B154" s="14">
-        <v>13.3256</v>
+        <v>13.5523</v>
       </c>
       <c r="C154" s="15">
-        <v>0.93</v>
+        <v>-0.16</v>
       </c>
       <c r="D154" s="16">
-        <v>11511148</v>
+        <v>12778173</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
@@ -3591,13 +3609,13 @@
         <v>160</v>
       </c>
       <c r="B155" s="14">
-        <v>13.2028</v>
+        <v>13.5734</v>
       </c>
       <c r="C155" s="15">
-        <v>-0.53</v>
+        <v>0.35</v>
       </c>
       <c r="D155" s="16">
-        <v>11462549</v>
+        <v>12525374</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
@@ -3607,13 +3625,13 @@
         <v>161</v>
       </c>
       <c r="B156" s="14">
-        <v>13.2731</v>
+        <v>13.5259</v>
       </c>
       <c r="C156" s="15">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="D156" s="16">
-        <v>11252942</v>
+        <v>12222638</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
@@ -3623,13 +3641,13 @@
         <v>162</v>
       </c>
       <c r="B157" s="14">
-        <v>13.2446</v>
+        <v>13.4447</v>
       </c>
       <c r="C157" s="15">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="D157" s="16">
-        <v>11240222</v>
+        <v>11902533</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
@@ -3639,13 +3657,13 @@
         <v>163</v>
       </c>
       <c r="B158" s="14">
-        <v>13.1508</v>
+        <v>13.4005</v>
       </c>
       <c r="C158" s="15">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="D158" s="16">
-        <v>11279869</v>
+        <v>11564711</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
@@ -3655,13 +3673,13 @@
         <v>164</v>
       </c>
       <c r="B159" s="14">
-        <v>13.0979</v>
+        <v>13.3707</v>
       </c>
       <c r="C159" s="15">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
       <c r="D159" s="16">
-        <v>11319939</v>
+        <v>11491616</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
@@ -3671,13 +3689,13 @@
         <v>165</v>
       </c>
       <c r="B160" s="14">
-        <v>13.1255</v>
+        <v>13.3256</v>
       </c>
       <c r="C160" s="15">
-        <v>0.31</v>
+        <v>0.93</v>
       </c>
       <c r="D160" s="16">
-        <v>11273680</v>
+        <v>11511148</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
@@ -3687,13 +3705,13 @@
         <v>166</v>
       </c>
       <c r="B161" s="14">
-        <v>13.0855</v>
+        <v>13.2028</v>
       </c>
       <c r="C161" s="15">
-        <v>-1</v>
+        <v>-0.53</v>
       </c>
       <c r="D161" s="16">
-        <v>10907008</v>
+        <v>11462549</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
@@ -3703,13 +3721,13 @@
         <v>167</v>
       </c>
       <c r="B162" s="14">
-        <v>13.2179</v>
+        <v>13.2731</v>
       </c>
       <c r="C162" s="15">
-        <v>-0.62</v>
+        <v>0.22</v>
       </c>
       <c r="D162" s="16">
-        <v>10664204</v>
+        <v>11252942</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
@@ -3719,13 +3737,13 @@
         <v>168</v>
       </c>
       <c r="B163" s="14">
-        <v>13.3002</v>
+        <v>13.2446</v>
       </c>
       <c r="C163" s="15">
-        <v>0.97</v>
+        <v>0.71</v>
       </c>
       <c r="D163" s="16">
-        <v>9876428</v>
+        <v>11240222</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
@@ -3735,13 +3753,13 @@
         <v>169</v>
       </c>
       <c r="B164" s="14">
-        <v>13.1727</v>
+        <v>13.1508</v>
       </c>
       <c r="C164" s="15">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="D164" s="16">
-        <v>8896695</v>
+        <v>11279869</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
@@ -3751,13 +3769,13 @@
         <v>170</v>
       </c>
       <c r="B165" s="14">
-        <v>13.1256</v>
+        <v>13.0979</v>
       </c>
       <c r="C165" s="15">
-        <v>0.31</v>
+        <v>-0.21</v>
       </c>
       <c r="D165" s="16">
-        <v>8738282</v>
+        <v>11319939</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
@@ -3767,13 +3785,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="14">
-        <v>13.0849</v>
+        <v>13.1255</v>
       </c>
       <c r="C166" s="15">
-        <v>-0.59</v>
+        <v>0.31</v>
       </c>
       <c r="D166" s="16">
-        <v>8668100</v>
+        <v>11273680</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
@@ -3783,13 +3801,13 @@
         <v>172</v>
       </c>
       <c r="B167" s="14">
-        <v>13.1621</v>
+        <v>13.0855</v>
       </c>
       <c r="C167" s="15">
-        <v>0.27</v>
+        <v>-1</v>
       </c>
       <c r="D167" s="16">
-        <v>8981828</v>
+        <v>10907008</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
@@ -3799,13 +3817,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="14">
-        <v>13.1268</v>
+        <v>13.2179</v>
       </c>
       <c r="C168" s="15">
-        <v>0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="D168" s="16">
-        <v>7580892</v>
+        <v>10664204</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
@@ -3815,13 +3833,13 @@
         <v>174</v>
       </c>
       <c r="B169" s="14">
-        <v>13.0564</v>
+        <v>13.3002</v>
       </c>
       <c r="C169" s="15">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="D169" s="16">
-        <v>7496759</v>
+        <v>9876428</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
@@ -3831,13 +3849,13 @@
         <v>175</v>
       </c>
       <c r="B170" s="14">
-        <v>13.0298</v>
+        <v>13.1727</v>
       </c>
       <c r="C170" s="15">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="D170" s="16">
-        <v>7405096</v>
+        <v>8896695</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
@@ -3847,13 +3865,13 @@
         <v>176</v>
       </c>
       <c r="B171" s="14">
-        <v>13.0006</v>
+        <v>13.1256</v>
       </c>
       <c r="C171" s="15">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="D171" s="16">
-        <v>7348884</v>
+        <v>8738282</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
@@ -3863,13 +3881,13 @@
         <v>177</v>
       </c>
       <c r="B172" s="14">
-        <v>12.9666</v>
+        <v>13.0849</v>
       </c>
       <c r="C172" s="15">
-        <v>1.15</v>
+        <v>-0.59</v>
       </c>
       <c r="D172" s="16">
-        <v>7204621</v>
+        <v>8668100</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
@@ -3879,13 +3897,13 @@
         <v>178</v>
       </c>
       <c r="B173" s="14">
-        <v>12.8192</v>
+        <v>13.1621</v>
       </c>
       <c r="C173" s="15">
-        <v>-0.67</v>
+        <v>0.27</v>
       </c>
       <c r="D173" s="16">
-        <v>6739403</v>
+        <v>8981828</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
@@ -3895,13 +3913,13 @@
         <v>179</v>
       </c>
       <c r="B174" s="14">
-        <v>12.9052</v>
+        <v>13.1268</v>
       </c>
       <c r="C174" s="15">
-        <v>0.91</v>
+        <v>0.54</v>
       </c>
       <c r="D174" s="16">
-        <v>6150440</v>
+        <v>7580892</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
@@ -3911,13 +3929,13 @@
         <v>180</v>
       </c>
       <c r="B175" s="14">
-        <v>12.7893</v>
+        <v>13.0564</v>
       </c>
       <c r="C175" s="15">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="D175" s="16">
-        <v>5477565</v>
+        <v>7496759</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="12"/>
@@ -3927,13 +3945,13 @@
         <v>181</v>
       </c>
       <c r="B176" s="14">
-        <v>12.7476</v>
+        <v>13.0298</v>
       </c>
       <c r="C176" s="15">
-        <v>-0.03</v>
+        <v>0.23</v>
       </c>
       <c r="D176" s="16">
-        <v>4610342</v>
+        <v>7405096</v>
       </c>
       <c r="E176" s="12"/>
       <c r="F176" s="12"/>
@@ -3943,13 +3961,13 @@
         <v>182</v>
       </c>
       <c r="B177" s="14">
-        <v>12.7519</v>
+        <v>13.0006</v>
       </c>
       <c r="C177" s="15">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="D177" s="16">
-        <v>4446149</v>
+        <v>7348884</v>
       </c>
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
@@ -3959,13 +3977,13 @@
         <v>183</v>
       </c>
       <c r="B178" s="14">
-        <v>12.6636</v>
+        <v>12.9666</v>
       </c>
       <c r="C178" s="15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="D178" s="16">
-        <v>4373755</v>
+        <v>7204621</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
@@ -3975,13 +3993,13 @@
         <v>184</v>
       </c>
       <c r="B179" s="14">
-        <v>12.5179</v>
+        <v>12.8192</v>
       </c>
       <c r="C179" s="15">
-        <v>2.49</v>
+        <v>-0.67</v>
       </c>
       <c r="D179" s="16">
-        <v>4232302</v>
+        <v>6739403</v>
       </c>
       <c r="E179" s="12"/>
       <c r="F179" s="12"/>
@@ -3991,13 +4009,13 @@
         <v>185</v>
       </c>
       <c r="B180" s="14">
-        <v>12.214</v>
+        <v>12.9052</v>
       </c>
       <c r="C180" s="15">
-        <v>-1.27</v>
+        <v>0.91</v>
       </c>
       <c r="D180" s="16">
-        <v>4038721</v>
+        <v>6150440</v>
       </c>
       <c r="E180" s="12"/>
       <c r="F180" s="12"/>
@@ -4007,13 +4025,13 @@
         <v>186</v>
       </c>
       <c r="B181" s="14">
-        <v>12.3707</v>
+        <v>12.7893</v>
       </c>
       <c r="C181" s="15">
-        <v>-0.87</v>
+        <v>0.33</v>
       </c>
       <c r="D181" s="16">
-        <v>3942311</v>
+        <v>5477565</v>
       </c>
       <c r="E181" s="12"/>
       <c r="F181" s="12"/>
@@ -4023,13 +4041,13 @@
         <v>187</v>
       </c>
       <c r="B182" s="14">
-        <v>12.4788</v>
+        <v>12.7476</v>
       </c>
       <c r="C182" s="15">
-        <v>0.33</v>
+        <v>-0.03</v>
       </c>
       <c r="D182" s="16">
-        <v>3892723</v>
+        <v>4610342</v>
       </c>
       <c r="E182" s="12"/>
       <c r="F182" s="12"/>
@@ -4039,13 +4057,13 @@
         <v>188</v>
       </c>
       <c r="B183" s="14">
-        <v>12.4379</v>
+        <v>12.7519</v>
       </c>
       <c r="C183" s="15">
-        <v>2.22</v>
+        <v>0.7</v>
       </c>
       <c r="D183" s="16">
-        <v>3848519</v>
+        <v>4446149</v>
       </c>
       <c r="E183" s="12"/>
       <c r="F183" s="12"/>
@@ -4055,13 +4073,13 @@
         <v>189</v>
       </c>
       <c r="B184" s="14">
-        <v>12.1674</v>
+        <v>12.6636</v>
       </c>
       <c r="C184" s="15">
-        <v>0.53</v>
+        <v>1.16</v>
       </c>
       <c r="D184" s="16">
-        <v>3819107</v>
+        <v>4373755</v>
       </c>
       <c r="E184" s="12"/>
       <c r="F184" s="12"/>
@@ -4071,13 +4089,13 @@
         <v>190</v>
       </c>
       <c r="B185" s="14">
-        <v>12.1034</v>
+        <v>12.5179</v>
       </c>
       <c r="C185" s="15">
-        <v>0.15</v>
+        <v>2.49</v>
       </c>
       <c r="D185" s="16">
-        <v>3631676</v>
+        <v>4232302</v>
       </c>
       <c r="E185" s="12"/>
       <c r="F185" s="12"/>
@@ -4087,13 +4105,13 @@
         <v>191</v>
       </c>
       <c r="B186" s="14">
-        <v>12.0853</v>
+        <v>12.214</v>
       </c>
       <c r="C186" s="15">
-        <v>0.92</v>
+        <v>-1.27</v>
       </c>
       <c r="D186" s="16">
-        <v>3361434</v>
+        <v>4038721</v>
       </c>
       <c r="E186" s="12"/>
       <c r="F186" s="12"/>
@@ -4103,13 +4121,13 @@
         <v>192</v>
       </c>
       <c r="B187" s="14">
-        <v>11.9757</v>
+        <v>12.3707</v>
       </c>
       <c r="C187" s="15">
-        <v>0.41</v>
+        <v>-0.87</v>
       </c>
       <c r="D187" s="16">
-        <v>2938660</v>
+        <v>3942311</v>
       </c>
       <c r="E187" s="12"/>
       <c r="F187" s="12"/>
@@ -4119,13 +4137,13 @@
         <v>193</v>
       </c>
       <c r="B188" s="14">
-        <v>11.9265</v>
+        <v>12.4788</v>
       </c>
       <c r="C188" s="15">
-        <v>-0.67</v>
+        <v>0.33</v>
       </c>
       <c r="D188" s="16">
-        <v>2728134</v>
+        <v>3892723</v>
       </c>
       <c r="E188" s="12"/>
       <c r="F188" s="12"/>
@@ -4135,13 +4153,13 @@
         <v>194</v>
       </c>
       <c r="B189" s="14">
-        <v>12.0069</v>
+        <v>12.4379</v>
       </c>
       <c r="C189" s="15">
-        <v>0.2</v>
+        <v>2.22</v>
       </c>
       <c r="D189" s="16">
-        <v>2719630</v>
+        <v>3848519</v>
       </c>
       <c r="E189" s="12"/>
       <c r="F189" s="12"/>
@@ -4151,13 +4169,13 @@
         <v>195</v>
       </c>
       <c r="B190" s="14">
-        <v>11.9827</v>
+        <v>12.1674</v>
       </c>
       <c r="C190" s="15">
-        <v>-0.88</v>
+        <v>0.53</v>
       </c>
       <c r="D190" s="16">
-        <v>2688147</v>
+        <v>3819107</v>
       </c>
       <c r="E190" s="12"/>
       <c r="F190" s="12"/>
@@ -4167,13 +4185,13 @@
         <v>196</v>
       </c>
       <c r="B191" s="14">
-        <v>12.0885</v>
+        <v>12.1034</v>
       </c>
       <c r="C191" s="15">
-        <v>-0.57</v>
+        <v>0.15</v>
       </c>
       <c r="D191" s="16">
-        <v>2609918</v>
+        <v>3631676</v>
       </c>
       <c r="E191" s="12"/>
       <c r="F191" s="12"/>
@@ -4183,13 +4201,13 @@
         <v>197</v>
       </c>
       <c r="B192" s="14">
-        <v>12.1577</v>
+        <v>12.0853</v>
       </c>
       <c r="C192" s="15">
-        <v>-0.95</v>
+        <v>0.92</v>
       </c>
       <c r="D192" s="16">
-        <v>2382996</v>
+        <v>3361434</v>
       </c>
       <c r="E192" s="12"/>
       <c r="F192" s="12"/>
@@ -4199,13 +4217,13 @@
         <v>198</v>
       </c>
       <c r="B193" s="14">
-        <v>12.2745</v>
+        <v>11.9757</v>
       </c>
       <c r="C193" s="15">
-        <v>-0.52</v>
+        <v>0.41</v>
       </c>
       <c r="D193" s="16">
-        <v>2331599</v>
+        <v>2938660</v>
       </c>
       <c r="E193" s="12"/>
       <c r="F193" s="12"/>
@@ -4215,13 +4233,13 @@
         <v>199</v>
       </c>
       <c r="B194" s="14">
-        <v>12.3391</v>
+        <v>11.9265</v>
       </c>
       <c r="C194" s="15">
-        <v>-0.61</v>
+        <v>-0.67</v>
       </c>
       <c r="D194" s="16">
-        <v>2255473</v>
+        <v>2728134</v>
       </c>
       <c r="E194" s="12"/>
       <c r="F194" s="12"/>
@@ -4231,13 +4249,13 @@
         <v>200</v>
       </c>
       <c r="B195" s="14">
-        <v>12.4146</v>
+        <v>12.0069</v>
       </c>
       <c r="C195" s="15">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="D195" s="16">
-        <v>2190337</v>
+        <v>2719630</v>
       </c>
       <c r="E195" s="12"/>
       <c r="F195" s="12"/>
@@ -4247,13 +4265,13 @@
         <v>201</v>
       </c>
       <c r="B196" s="14">
-        <v>12.2069</v>
+        <v>11.9827</v>
       </c>
       <c r="C196" s="15">
-        <v>0.06</v>
+        <v>-0.88</v>
       </c>
       <c r="D196" s="16">
-        <v>2136945</v>
+        <v>2688147</v>
       </c>
       <c r="E196" s="12"/>
       <c r="F196" s="12"/>
@@ -4263,13 +4281,13 @@
         <v>202</v>
       </c>
       <c r="B197" s="14">
-        <v>12.2</v>
+        <v>12.0885</v>
       </c>
       <c r="C197" s="15">
-        <v>-0.03</v>
+        <v>-0.57</v>
       </c>
       <c r="D197" s="16">
-        <v>1912961</v>
+        <v>2609918</v>
       </c>
       <c r="E197" s="12"/>
       <c r="F197" s="12"/>
@@ -4279,13 +4297,13 @@
         <v>203</v>
       </c>
       <c r="B198" s="14">
-        <v>12.2039</v>
+        <v>12.1577</v>
       </c>
       <c r="C198" s="15">
-        <v>1.06</v>
+        <v>-0.95</v>
       </c>
       <c r="D198" s="16">
-        <v>1647911</v>
+        <v>2382996</v>
       </c>
       <c r="E198" s="12"/>
       <c r="F198" s="12"/>
@@ -4295,13 +4313,13 @@
         <v>204</v>
       </c>
       <c r="B199" s="14">
-        <v>12.0758</v>
+        <v>12.2745</v>
       </c>
       <c r="C199" s="15">
-        <v>0.22</v>
+        <v>-0.52</v>
       </c>
       <c r="D199" s="16">
-        <v>1294332</v>
+        <v>2331599</v>
       </c>
       <c r="E199" s="12"/>
       <c r="F199" s="12"/>
@@ -4311,13 +4329,13 @@
         <v>205</v>
       </c>
       <c r="B200" s="14">
-        <v>12.0493</v>
+        <v>12.3391</v>
       </c>
       <c r="C200" s="15">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="D200" s="16">
-        <v>1062837</v>
+        <v>2255473</v>
       </c>
       <c r="E200" s="12"/>
       <c r="F200" s="12"/>
@@ -4327,13 +4345,13 @@
         <v>206</v>
       </c>
       <c r="B201" s="14">
-        <v>12.0181</v>
+        <v>12.4146</v>
       </c>
       <c r="C201" s="15">
-        <v>0.78</v>
+        <v>1.7</v>
       </c>
       <c r="D201" s="16">
-        <v>928815</v>
+        <v>2190337</v>
       </c>
       <c r="E201" s="12"/>
       <c r="F201" s="12"/>
@@ -4343,13 +4361,13 @@
         <v>207</v>
       </c>
       <c r="B202" s="14">
-        <v>11.9249</v>
+        <v>12.2069</v>
       </c>
       <c r="C202" s="15">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="D202" s="16">
-        <v>848138</v>
+        <v>2136945</v>
       </c>
       <c r="E202" s="12"/>
       <c r="F202" s="12"/>
@@ -4359,13 +4377,13 @@
         <v>208</v>
       </c>
       <c r="B203" s="14">
-        <v>11.8533</v>
+        <v>12.2</v>
       </c>
       <c r="C203" s="15">
-        <v>-0.62</v>
+        <v>-0.03</v>
       </c>
       <c r="D203" s="16">
-        <v>767931</v>
+        <v>1912961</v>
       </c>
       <c r="E203" s="12"/>
       <c r="F203" s="12"/>
@@ -4375,13 +4393,13 @@
         <v>209</v>
       </c>
       <c r="B204" s="14">
-        <v>11.9267</v>
+        <v>12.2039</v>
       </c>
       <c r="C204" s="15">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="D204" s="16">
-        <v>661974</v>
+        <v>1647911</v>
       </c>
       <c r="E204" s="12"/>
       <c r="F204" s="12"/>
@@ -4391,13 +4409,13 @@
         <v>210</v>
       </c>
       <c r="B205" s="14">
-        <v>11.83</v>
+        <v>12.0758</v>
       </c>
       <c r="C205" s="15">
-        <v>-0.17</v>
+        <v>0.22</v>
       </c>
       <c r="D205" s="16">
-        <v>640811</v>
+        <v>1294332</v>
       </c>
       <c r="E205" s="12"/>
       <c r="F205" s="12"/>
@@ -4407,13 +4425,13 @@
         <v>211</v>
       </c>
       <c r="B206" s="14">
-        <v>11.85</v>
+        <v>12.0493</v>
       </c>
       <c r="C206" s="15">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="D206" s="16">
-        <v>612687</v>
+        <v>1062837</v>
       </c>
       <c r="E206" s="12"/>
       <c r="F206" s="12"/>
@@ -4423,13 +4441,13 @@
         <v>212</v>
       </c>
       <c r="B207" s="14">
-        <v>11.8</v>
+        <v>12.0181</v>
       </c>
       <c r="C207" s="15">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="D207" s="16">
-        <v>605714</v>
+        <v>928815</v>
       </c>
       <c r="E207" s="12"/>
       <c r="F207" s="12"/>
@@ -4439,13 +4457,13 @@
         <v>213</v>
       </c>
       <c r="B208" s="14">
-        <v>11.753</v>
+        <v>11.9249</v>
       </c>
       <c r="C208" s="15">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="D208" s="16">
-        <v>584101</v>
+        <v>848138</v>
       </c>
       <c r="E208" s="12"/>
       <c r="F208" s="12"/>
@@ -4455,13 +4473,13 @@
         <v>214</v>
       </c>
       <c r="B209" s="14">
-        <v>11.715</v>
+        <v>11.8533</v>
       </c>
       <c r="C209" s="15">
-        <v>0.75</v>
+        <v>-0.62</v>
       </c>
       <c r="D209" s="16">
-        <v>534600</v>
+        <v>767931</v>
       </c>
       <c r="E209" s="12"/>
       <c r="F209" s="12"/>
@@ -4471,13 +4489,13 @@
         <v>215</v>
       </c>
       <c r="B210" s="14">
-        <v>11.628</v>
+        <v>11.9267</v>
       </c>
       <c r="C210" s="15">
-        <v>-0.36</v>
+        <v>0.82</v>
       </c>
       <c r="D210" s="16">
-        <v>396802</v>
+        <v>661974</v>
       </c>
       <c r="E210" s="12"/>
       <c r="F210" s="12"/>
@@ -4487,13 +4505,13 @@
         <v>216</v>
       </c>
       <c r="B211" s="14">
-        <v>11.67</v>
+        <v>11.83</v>
       </c>
       <c r="C211" s="15">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="D211" s="16">
-        <v>265881</v>
+        <v>640811</v>
       </c>
       <c r="E211" s="12"/>
       <c r="F211" s="12"/>
@@ -4503,13 +4521,13 @@
         <v>217</v>
       </c>
       <c r="B212" s="14">
-        <v>11.683</v>
+        <v>11.85</v>
       </c>
       <c r="C212" s="15">
-        <v>-0.18</v>
+        <v>0.42</v>
       </c>
       <c r="D212" s="16">
-        <v>244798</v>
+        <v>612687</v>
       </c>
       <c r="E212" s="12"/>
       <c r="F212" s="12"/>
@@ -4519,13 +4537,13 @@
         <v>218</v>
       </c>
       <c r="B213" s="14">
-        <v>11.704</v>
+        <v>11.8</v>
       </c>
       <c r="C213" s="15">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="D213" s="16">
-        <v>227751</v>
+        <v>605714</v>
       </c>
       <c r="E213" s="12"/>
       <c r="F213" s="12"/>
@@ -4535,13 +4553,13 @@
         <v>219</v>
       </c>
       <c r="B214" s="14">
-        <v>11.607</v>
+        <v>11.753</v>
       </c>
       <c r="C214" s="15">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="D214" s="16">
-        <v>214864</v>
+        <v>584101</v>
       </c>
       <c r="E214" s="12"/>
       <c r="F214" s="12"/>
@@ -4551,13 +4569,13 @@
         <v>220</v>
       </c>
       <c r="B215" s="14">
-        <v>11.604</v>
+        <v>11.715</v>
       </c>
       <c r="C215" s="15">
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
       <c r="D215" s="16">
-        <v>173999</v>
+        <v>534600</v>
       </c>
       <c r="E215" s="12"/>
       <c r="F215" s="12"/>
@@ -4567,13 +4585,13 @@
         <v>221</v>
       </c>
       <c r="B216" s="14">
-        <v>11.496</v>
+        <v>11.628</v>
       </c>
       <c r="C216" s="15">
-        <v>1.43</v>
+        <v>-0.36</v>
       </c>
       <c r="D216" s="16">
-        <v>158951</v>
+        <v>396802</v>
       </c>
       <c r="E216" s="12"/>
       <c r="F216" s="12"/>
@@ -4583,13 +4601,13 @@
         <v>222</v>
       </c>
       <c r="B217" s="14">
-        <v>11.334</v>
+        <v>11.67</v>
       </c>
       <c r="C217" s="15">
-        <v>3.6</v>
+        <v>-0.11</v>
       </c>
       <c r="D217" s="16">
-        <v>153245</v>
+        <v>265881</v>
       </c>
       <c r="E217" s="12"/>
       <c r="F217" s="12"/>
@@ -4599,13 +4617,13 @@
         <v>223</v>
       </c>
       <c r="B218" s="14">
-        <v>10.94</v>
+        <v>11.683</v>
       </c>
       <c r="C218" s="15">
-        <v>0.52</v>
+        <v>-0.18</v>
       </c>
       <c r="D218" s="16">
-        <v>150460</v>
+        <v>244798</v>
       </c>
       <c r="E218" s="12"/>
       <c r="F218" s="12"/>
@@ -4615,13 +4633,13 @@
         <v>224</v>
       </c>
       <c r="B219" s="14">
-        <v>10.884</v>
+        <v>11.704</v>
       </c>
       <c r="C219" s="15">
-        <v>1.57</v>
+        <v>0.84</v>
       </c>
       <c r="D219" s="16">
-        <v>149975</v>
+        <v>227751</v>
       </c>
       <c r="E219" s="12"/>
       <c r="F219" s="12"/>
@@ -4631,13 +4649,13 @@
         <v>225</v>
       </c>
       <c r="B220" s="14">
-        <v>10.716</v>
+        <v>11.607</v>
       </c>
       <c r="C220" s="15">
-        <v>0.37</v>
+        <v>0.03</v>
       </c>
       <c r="D220" s="16">
-        <v>146802</v>
+        <v>214864</v>
       </c>
       <c r="E220" s="12"/>
       <c r="F220" s="12"/>
@@ -4647,13 +4665,13 @@
         <v>226</v>
       </c>
       <c r="B221" s="14">
-        <v>10.677</v>
+        <v>11.604</v>
       </c>
       <c r="C221" s="15">
-        <v>-0.43</v>
+        <v>0.94</v>
       </c>
       <c r="D221" s="16">
-        <v>55851</v>
+        <v>173999</v>
       </c>
       <c r="E221" s="12"/>
       <c r="F221" s="12"/>
@@ -4663,13 +4681,13 @@
         <v>227</v>
       </c>
       <c r="B222" s="14">
-        <v>10.723</v>
+        <v>11.496</v>
       </c>
       <c r="C222" s="15">
-        <v>-0.94</v>
+        <v>1.43</v>
       </c>
       <c r="D222" s="16">
-        <v>55484</v>
+        <v>158951</v>
       </c>
       <c r="E222" s="12"/>
       <c r="F222" s="12"/>
@@ -4679,13 +4697,13 @@
         <v>228</v>
       </c>
       <c r="B223" s="14">
-        <v>10.825</v>
+        <v>11.334</v>
       </c>
       <c r="C223" s="15">
-        <v>-1.17</v>
+        <v>3.6</v>
       </c>
       <c r="D223" s="16">
-        <v>53984</v>
+        <v>153245</v>
       </c>
       <c r="E223" s="12"/>
       <c r="F223" s="12"/>
@@ -4695,13 +4713,13 @@
         <v>229</v>
       </c>
       <c r="B224" s="14">
-        <v>10.953</v>
+        <v>10.94</v>
       </c>
       <c r="C224" s="15">
-        <v>-0.73</v>
+        <v>0.52</v>
       </c>
       <c r="D224" s="16">
-        <v>49996</v>
+        <v>150460</v>
       </c>
       <c r="E224" s="12"/>
       <c r="F224" s="12"/>
@@ -4711,13 +4729,13 @@
         <v>230</v>
       </c>
       <c r="B225" s="14">
-        <v>11.033</v>
+        <v>10.884</v>
       </c>
       <c r="C225" s="15">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="D225" s="16">
-        <v>46812</v>
+        <v>149975</v>
       </c>
       <c r="E225" s="12"/>
       <c r="F225" s="12"/>
@@ -4727,13 +4745,13 @@
         <v>231</v>
       </c>
       <c r="B226" s="14">
-        <v>10.914</v>
+        <v>10.716</v>
       </c>
       <c r="C226" s="15">
-        <v>1.9</v>
+        <v>0.37</v>
       </c>
       <c r="D226" s="16">
-        <v>46623</v>
+        <v>146802</v>
       </c>
       <c r="E226" s="12"/>
       <c r="F226" s="12"/>
@@ -4743,13 +4761,13 @@
         <v>232</v>
       </c>
       <c r="B227" s="14">
-        <v>10.711</v>
+        <v>10.677</v>
       </c>
       <c r="C227" s="15">
-        <v>-0.5</v>
+        <v>-0.43</v>
       </c>
       <c r="D227" s="16">
-        <v>43430</v>
+        <v>55851</v>
       </c>
       <c r="E227" s="12"/>
       <c r="F227" s="12"/>
@@ -4759,13 +4777,13 @@
         <v>233</v>
       </c>
       <c r="B228" s="14">
-        <v>10.765</v>
+        <v>10.723</v>
       </c>
       <c r="C228" s="15">
-        <v>0.8</v>
+        <v>-0.94</v>
       </c>
       <c r="D228" s="16">
-        <v>40192</v>
+        <v>55484</v>
       </c>
       <c r="E228" s="12"/>
       <c r="F228" s="12"/>
@@ -4775,13 +4793,13 @@
         <v>234</v>
       </c>
       <c r="B229" s="14">
-        <v>10.68</v>
+        <v>10.825</v>
       </c>
       <c r="C229" s="15">
-        <v>0.78</v>
+        <v>-1.17</v>
       </c>
       <c r="D229" s="16">
-        <v>40205</v>
+        <v>53984</v>
       </c>
       <c r="E229" s="12"/>
       <c r="F229" s="12"/>
@@ -4791,13 +4809,13 @@
         <v>235</v>
       </c>
       <c r="B230" s="14">
-        <v>10.597</v>
+        <v>10.953</v>
       </c>
       <c r="C230" s="15">
-        <v>-0.13</v>
+        <v>-0.73</v>
       </c>
       <c r="D230" s="16">
-        <v>39767</v>
+        <v>49996</v>
       </c>
       <c r="E230" s="12"/>
       <c r="F230" s="12"/>
@@ -4807,13 +4825,13 @@
         <v>236</v>
       </c>
       <c r="B231" s="14">
-        <v>10.611</v>
+        <v>11.033</v>
       </c>
       <c r="C231" s="15">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="D231" s="16">
-        <v>40015</v>
+        <v>46812</v>
       </c>
       <c r="E231" s="12"/>
       <c r="F231" s="12"/>
@@ -4823,13 +4841,13 @@
         <v>237</v>
       </c>
       <c r="B232" s="14">
-        <v>10.532</v>
+        <v>10.914</v>
       </c>
       <c r="C232" s="15">
-        <v>1.07</v>
+        <v>1.9</v>
       </c>
       <c r="D232" s="16">
-        <v>39952</v>
+        <v>46623</v>
       </c>
       <c r="E232" s="12"/>
       <c r="F232" s="12"/>
@@ -4839,13 +4857,13 @@
         <v>238</v>
       </c>
       <c r="B233" s="14">
-        <v>10.421</v>
+        <v>10.711</v>
       </c>
       <c r="C233" s="15">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="D233" s="16">
-        <v>40169</v>
+        <v>43430</v>
       </c>
       <c r="E233" s="12"/>
       <c r="F233" s="12"/>
@@ -4855,13 +4873,13 @@
         <v>239</v>
       </c>
       <c r="B234" s="14">
-        <v>10.472</v>
+        <v>10.765</v>
       </c>
       <c r="C234" s="15">
-        <v>-0.32</v>
+        <v>0.8</v>
       </c>
       <c r="D234" s="16">
-        <v>38333</v>
+        <v>40192</v>
       </c>
       <c r="E234" s="12"/>
       <c r="F234" s="12"/>
@@ -4871,13 +4889,13 @@
         <v>240</v>
       </c>
       <c r="B235" s="14">
-        <v>10.506</v>
+        <v>10.68</v>
       </c>
       <c r="C235" s="15">
-        <v>-0.46</v>
+        <v>0.78</v>
       </c>
       <c r="D235" s="16">
-        <v>38694</v>
+        <v>40205</v>
       </c>
       <c r="E235" s="12"/>
       <c r="F235" s="12"/>
@@ -4887,13 +4905,13 @@
         <v>241</v>
       </c>
       <c r="B236" s="14">
-        <v>10.554</v>
+        <v>10.597</v>
       </c>
       <c r="C236" s="15">
-        <v>0.23</v>
+        <v>-0.13</v>
       </c>
       <c r="D236" s="16">
-        <v>37907</v>
+        <v>39767</v>
       </c>
       <c r="E236" s="12"/>
       <c r="F236" s="12"/>
@@ -4903,13 +4921,13 @@
         <v>242</v>
       </c>
       <c r="B237" s="14">
-        <v>10.53</v>
+        <v>10.611</v>
       </c>
       <c r="C237" s="15">
-        <v>0.17</v>
+        <v>0.75</v>
       </c>
       <c r="D237" s="16">
-        <v>36650</v>
+        <v>40015</v>
       </c>
       <c r="E237" s="12"/>
       <c r="F237" s="12"/>
@@ -4919,13 +4937,13 @@
         <v>243</v>
       </c>
       <c r="B238" s="14">
-        <v>10.512</v>
+        <v>10.532</v>
       </c>
       <c r="C238" s="15">
-        <v>-0.19</v>
+        <v>1.07</v>
       </c>
       <c r="D238" s="16">
-        <v>34921</v>
+        <v>39952</v>
       </c>
       <c r="E238" s="12"/>
       <c r="F238" s="12"/>
@@ -4935,13 +4953,13 @@
         <v>244</v>
       </c>
       <c r="B239" s="14">
-        <v>10.532</v>
+        <v>10.421</v>
       </c>
       <c r="C239" s="15">
-        <v>-0.64</v>
+        <v>-0.49</v>
       </c>
       <c r="D239" s="16">
-        <v>33255</v>
+        <v>40169</v>
       </c>
       <c r="E239" s="12"/>
       <c r="F239" s="12"/>
@@ -4951,13 +4969,13 @@
         <v>245</v>
       </c>
       <c r="B240" s="14">
-        <v>10.6</v>
+        <v>10.472</v>
       </c>
       <c r="C240" s="15">
-        <v>0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="D240" s="16">
-        <v>32711</v>
+        <v>38333</v>
       </c>
       <c r="E240" s="12"/>
       <c r="F240" s="12"/>
@@ -4967,13 +4985,13 @@
         <v>246</v>
       </c>
       <c r="B241" s="14">
-        <v>10.54</v>
+        <v>10.506</v>
       </c>
       <c r="C241" s="15">
-        <v>-0.47</v>
+        <v>-0.46</v>
       </c>
       <c r="D241" s="16">
-        <v>33378</v>
+        <v>38694</v>
       </c>
       <c r="E241" s="12"/>
       <c r="F241" s="12"/>
@@ -4983,13 +5001,13 @@
         <v>247</v>
       </c>
       <c r="B242" s="14">
-        <v>10.59</v>
+        <v>10.554</v>
       </c>
       <c r="C242" s="15">
-        <v>0.48</v>
+        <v>0.23</v>
       </c>
       <c r="D242" s="16">
-        <v>34091</v>
+        <v>37907</v>
       </c>
       <c r="E242" s="12"/>
       <c r="F242" s="12"/>
@@ -4999,13 +5017,13 @@
         <v>248</v>
       </c>
       <c r="B243" s="14">
-        <v>10.539</v>
+        <v>10.53</v>
       </c>
       <c r="C243" s="15">
-        <v>0.59</v>
+        <v>0.17</v>
       </c>
       <c r="D243" s="16">
-        <v>34184</v>
+        <v>36650</v>
       </c>
       <c r="E243" s="12"/>
       <c r="F243" s="12"/>
@@ -5015,13 +5033,13 @@
         <v>249</v>
       </c>
       <c r="B244" s="14">
-        <v>10.477</v>
+        <v>10.512</v>
       </c>
       <c r="C244" s="15">
-        <v>0.53</v>
+        <v>-0.19</v>
       </c>
       <c r="D244" s="16">
-        <v>34385</v>
+        <v>34921</v>
       </c>
       <c r="E244" s="12"/>
       <c r="F244" s="12"/>
@@ -5031,13 +5049,13 @@
         <v>250</v>
       </c>
       <c r="B245" s="14">
-        <v>10.422</v>
+        <v>10.532</v>
       </c>
       <c r="C245" s="15">
-        <v>-0.55</v>
+        <v>-0.64</v>
       </c>
       <c r="D245" s="16">
-        <v>33911</v>
+        <v>33255</v>
       </c>
       <c r="E245" s="12"/>
       <c r="F245" s="12"/>
@@ -5047,13 +5065,13 @@
         <v>251</v>
       </c>
       <c r="B246" s="14">
-        <v>10.48</v>
+        <v>10.6</v>
       </c>
       <c r="C246" s="15">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="D246" s="16">
-        <v>33624</v>
+        <v>32711</v>
       </c>
       <c r="E246" s="12"/>
       <c r="F246" s="12"/>
@@ -5063,13 +5081,13 @@
         <v>252</v>
       </c>
       <c r="B247" s="14">
-        <v>10.402</v>
+        <v>10.54</v>
       </c>
       <c r="C247" s="15">
-        <v>-0.35</v>
+        <v>-0.47</v>
       </c>
       <c r="D247" s="16">
-        <v>22494</v>
+        <v>33378</v>
       </c>
       <c r="E247" s="12"/>
       <c r="F247" s="12"/>
@@ -5079,13 +5097,13 @@
         <v>253</v>
       </c>
       <c r="B248" s="14">
-        <v>10.438</v>
+        <v>10.59</v>
       </c>
       <c r="C248" s="15">
-        <v>-0.95</v>
+        <v>0.48</v>
       </c>
       <c r="D248" s="16">
-        <v>16869</v>
+        <v>34091</v>
       </c>
       <c r="E248" s="12"/>
       <c r="F248" s="12"/>
@@ -5095,13 +5113,13 @@
         <v>254</v>
       </c>
       <c r="B249" s="14">
-        <v>10.538</v>
+        <v>10.539</v>
       </c>
       <c r="C249" s="15">
-        <v>0.08</v>
+        <v>0.59</v>
       </c>
       <c r="D249" s="16">
-        <v>16869</v>
+        <v>34184</v>
       </c>
       <c r="E249" s="12"/>
       <c r="F249" s="12"/>
@@ -5111,13 +5129,13 @@
         <v>255</v>
       </c>
       <c r="B250" s="14">
-        <v>10.53</v>
+        <v>10.477</v>
       </c>
       <c r="C250" s="15">
-        <v>-0.38</v>
+        <v>0.53</v>
       </c>
       <c r="D250" s="16">
-        <v>17496</v>
+        <v>34385</v>
       </c>
       <c r="E250" s="12"/>
       <c r="F250" s="12"/>
@@ -5127,13 +5145,13 @@
         <v>256</v>
       </c>
       <c r="B251" s="14">
-        <v>10.57</v>
+        <v>10.422</v>
       </c>
       <c r="C251" s="15">
-        <v>0.17</v>
+        <v>-0.55</v>
       </c>
       <c r="D251" s="16">
-        <v>17496</v>
+        <v>33911</v>
       </c>
       <c r="E251" s="12"/>
       <c r="F251" s="12"/>
@@ -5143,13 +5161,13 @@
         <v>257</v>
       </c>
       <c r="B252" s="14">
-        <v>10.552</v>
+        <v>10.48</v>
       </c>
       <c r="C252" s="15">
-        <v>0.06</v>
+        <v>0.75</v>
       </c>
       <c r="D252" s="16">
-        <v>18388</v>
+        <v>33624</v>
       </c>
       <c r="E252" s="12"/>
       <c r="F252" s="12"/>
@@ -5159,13 +5177,13 @@
         <v>258</v>
       </c>
       <c r="B253" s="14">
-        <v>10.546</v>
+        <v>10.402</v>
       </c>
       <c r="C253" s="15">
-        <v>-0.78</v>
+        <v>-0.35</v>
       </c>
       <c r="D253" s="16">
-        <v>18296</v>
+        <v>22494</v>
       </c>
       <c r="E253" s="12"/>
       <c r="F253" s="12"/>
@@ -5175,13 +5193,13 @@
         <v>259</v>
       </c>
       <c r="B254" s="14">
-        <v>10.629</v>
+        <v>10.438</v>
       </c>
       <c r="C254" s="15">
-        <v>-0.13</v>
+        <v>-0.95</v>
       </c>
       <c r="D254" s="16">
-        <v>18525</v>
+        <v>16869</v>
       </c>
       <c r="E254" s="12"/>
       <c r="F254" s="12"/>
@@ -5191,13 +5209,13 @@
         <v>260</v>
       </c>
       <c r="B255" s="14">
-        <v>10.643</v>
+        <v>10.538</v>
       </c>
       <c r="C255" s="15">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
       <c r="D255" s="16">
-        <v>18764</v>
+        <v>16869</v>
       </c>
       <c r="E255" s="12"/>
       <c r="F255" s="12"/>
@@ -5207,13 +5225,13 @@
         <v>261</v>
       </c>
       <c r="B256" s="14">
-        <v>10.603</v>
+        <v>10.53</v>
       </c>
       <c r="C256" s="15">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="D256" s="16">
-        <v>18783</v>
+        <v>17496</v>
       </c>
       <c r="E256" s="12"/>
       <c r="F256" s="12"/>
@@ -5223,13 +5241,13 @@
         <v>262</v>
       </c>
       <c r="B257" s="14">
-        <v>10.637</v>
+        <v>10.57</v>
       </c>
       <c r="C257" s="15">
-        <v>0.85</v>
+        <v>0.17</v>
       </c>
       <c r="D257" s="16">
-        <v>18552</v>
+        <v>17496</v>
       </c>
       <c r="E257" s="12"/>
       <c r="F257" s="12"/>
@@ -5239,13 +5257,13 @@
         <v>263</v>
       </c>
       <c r="B258" s="14">
-        <v>10.547</v>
+        <v>10.552</v>
       </c>
       <c r="C258" s="15">
-        <v>0.46</v>
+        <v>0.06</v>
       </c>
       <c r="D258" s="16">
-        <v>17764</v>
+        <v>18388</v>
       </c>
       <c r="E258" s="12"/>
       <c r="F258" s="12"/>
@@ -5255,13 +5273,13 @@
         <v>264</v>
       </c>
       <c r="B259" s="14">
-        <v>10.499</v>
+        <v>10.546</v>
       </c>
       <c r="C259" s="15">
-        <v>1.52</v>
+        <v>-0.78</v>
       </c>
       <c r="D259" s="16">
-        <v>14538</v>
+        <v>18296</v>
       </c>
       <c r="E259" s="12"/>
       <c r="F259" s="12"/>
@@ -5271,13 +5289,13 @@
         <v>265</v>
       </c>
       <c r="B260" s="14">
-        <v>10.342</v>
+        <v>10.629</v>
       </c>
       <c r="C260" s="15">
-        <v>0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="D260" s="16">
-        <v>9092</v>
+        <v>18525</v>
       </c>
       <c r="E260" s="12"/>
       <c r="F260" s="12"/>
@@ -5287,13 +5305,13 @@
         <v>266</v>
       </c>
       <c r="B261" s="14">
-        <v>10.327</v>
+        <v>10.643</v>
       </c>
       <c r="C261" s="15">
-        <v>-0.31</v>
+        <v>0.38</v>
       </c>
       <c r="D261" s="16">
-        <v>8762</v>
+        <v>18764</v>
       </c>
       <c r="E261" s="12"/>
       <c r="F261" s="12"/>
@@ -5303,13 +5321,13 @@
         <v>267</v>
       </c>
       <c r="B262" s="14">
-        <v>10.359</v>
+        <v>10.603</v>
       </c>
       <c r="C262" s="15">
-        <v>0.51</v>
+        <v>-0.32</v>
       </c>
       <c r="D262" s="16">
-        <v>8762</v>
+        <v>18783</v>
       </c>
       <c r="E262" s="12"/>
       <c r="F262" s="12"/>
@@ -5319,13 +5337,13 @@
         <v>268</v>
       </c>
       <c r="B263" s="14">
-        <v>10.306</v>
+        <v>10.637</v>
       </c>
       <c r="C263" s="15">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="D263" s="16">
-        <v>9357</v>
+        <v>18552</v>
       </c>
       <c r="E263" s="12"/>
       <c r="F263" s="12"/>
@@ -5335,13 +5353,13 @@
         <v>269</v>
       </c>
       <c r="B264" s="14">
-        <v>10.287</v>
+        <v>10.547</v>
       </c>
       <c r="C264" s="15">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="D264" s="16">
-        <v>9357</v>
+        <v>17764</v>
       </c>
       <c r="E264" s="12"/>
       <c r="F264" s="12"/>
@@ -5351,13 +5369,13 @@
         <v>270</v>
       </c>
       <c r="B265" s="14">
-        <v>10.214</v>
+        <v>10.499</v>
       </c>
       <c r="C265" s="15">
-        <v>0.64</v>
+        <v>1.52</v>
       </c>
       <c r="D265" s="16">
-        <v>9558</v>
+        <v>14538</v>
       </c>
       <c r="E265" s="12"/>
       <c r="F265" s="12"/>
@@ -5367,13 +5385,13 @@
         <v>271</v>
       </c>
       <c r="B266" s="14">
-        <v>10.149</v>
+        <v>10.342</v>
       </c>
       <c r="C266" s="15">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="D266" s="16">
-        <v>9616</v>
+        <v>9092</v>
       </c>
       <c r="E266" s="12"/>
       <c r="F266" s="12"/>
@@ -5383,13 +5401,13 @@
         <v>272</v>
       </c>
       <c r="B267" s="14">
-        <v>10.095</v>
+        <v>10.327</v>
       </c>
       <c r="C267" s="15">
-        <v>0.8</v>
+        <v>-0.31</v>
       </c>
       <c r="D267" s="16">
-        <v>10127</v>
+        <v>8762</v>
       </c>
       <c r="E267" s="12"/>
       <c r="F267" s="12"/>
@@ -5399,13 +5417,13 @@
         <v>273</v>
       </c>
       <c r="B268" s="14">
-        <v>10.015</v>
+        <v>10.359</v>
       </c>
       <c r="C268" s="15">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="D268" s="16">
-        <v>7988</v>
+        <v>8762</v>
       </c>
       <c r="E268" s="12"/>
       <c r="F268" s="12"/>
@@ -5415,13 +5433,13 @@
         <v>274</v>
       </c>
       <c r="B269" s="14">
-        <v>9.97</v>
+        <v>10.306</v>
       </c>
       <c r="C269" s="15">
-        <v>-0.31</v>
+        <v>0.19</v>
       </c>
       <c r="D269" s="16">
-        <v>8865</v>
+        <v>9357</v>
       </c>
       <c r="E269" s="12"/>
       <c r="F269" s="12"/>
@@ -5431,13 +5449,13 @@
         <v>275</v>
       </c>
       <c r="B270" s="14">
-        <v>10.001</v>
+        <v>10.287</v>
       </c>
       <c r="C270" s="15">
-        <v>0.18</v>
+        <v>0.72</v>
       </c>
       <c r="D270" s="16">
-        <v>2189</v>
+        <v>9357</v>
       </c>
       <c r="E270" s="12"/>
       <c r="F270" s="12"/>
@@ -5447,13 +5465,13 @@
         <v>276</v>
       </c>
       <c r="B271" s="14">
-        <v>9.983</v>
+        <v>10.214</v>
       </c>
       <c r="C271" s="15">
-        <v>-1.39</v>
+        <v>0.64</v>
       </c>
       <c r="D271" s="16">
-        <v>500</v>
+        <v>9558</v>
       </c>
       <c r="E271" s="12"/>
       <c r="F271" s="12"/>
@@ -5463,13 +5481,13 @@
         <v>277</v>
       </c>
       <c r="B272" s="14">
-        <v>10.124</v>
+        <v>10.149</v>
       </c>
       <c r="C272" s="15">
-        <v>1.24</v>
+        <v>0.54</v>
       </c>
       <c r="D272" s="16">
-        <v>500</v>
+        <v>9616</v>
       </c>
       <c r="E272" s="12"/>
       <c r="F272" s="12"/>
@@ -5479,29 +5497,125 @@
         <v>278</v>
       </c>
       <c r="B273" s="14">
-        <v>10</v>
-      </c>
-      <c r="C273" s="17" t="s">
-        <v>279</v>
+        <v>10.095</v>
+      </c>
+      <c r="C273" s="15">
+        <v>0.8</v>
       </c>
       <c r="D273" s="16">
-        <v>0</v>
+        <v>10127</v>
       </c>
       <c r="E273" s="12"/>
       <c r="F273" s="12"/>
     </row>
-    <row r="274" ht="35" customHeight="1">
-      <c r="A274" s="18" t="s">
+    <row r="274" s="12" customFormat="1">
+      <c r="A274" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B274" s="14">
+        <v>10.015</v>
+      </c>
+      <c r="C274" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="D274" s="16">
+        <v>7988</v>
+      </c>
+      <c r="E274" s="12"/>
+      <c r="F274" s="12"/>
+    </row>
+    <row r="275" s="12" customFormat="1">
+      <c r="A275" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="B274" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C274" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="D274" s="18" t="s">
-        <v>280</v>
+      <c r="B275" s="14">
+        <v>9.97</v>
+      </c>
+      <c r="C275" s="15">
+        <v>-0.31</v>
+      </c>
+      <c r="D275" s="16">
+        <v>8865</v>
+      </c>
+      <c r="E275" s="12"/>
+      <c r="F275" s="12"/>
+    </row>
+    <row r="276" s="12" customFormat="1">
+      <c r="A276" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B276" s="14">
+        <v>10.001</v>
+      </c>
+      <c r="C276" s="15">
+        <v>0.18</v>
+      </c>
+      <c r="D276" s="16">
+        <v>2189</v>
+      </c>
+      <c r="E276" s="12"/>
+      <c r="F276" s="12"/>
+    </row>
+    <row r="277" s="12" customFormat="1">
+      <c r="A277" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B277" s="14">
+        <v>9.983</v>
+      </c>
+      <c r="C277" s="15">
+        <v>-1.39</v>
+      </c>
+      <c r="D277" s="16">
+        <v>500</v>
+      </c>
+      <c r="E277" s="12"/>
+      <c r="F277" s="12"/>
+    </row>
+    <row r="278" s="12" customFormat="1">
+      <c r="A278" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B278" s="14">
+        <v>10.124</v>
+      </c>
+      <c r="C278" s="15">
+        <v>1.24</v>
+      </c>
+      <c r="D278" s="16">
+        <v>500</v>
+      </c>
+      <c r="E278" s="12"/>
+      <c r="F278" s="12"/>
+    </row>
+    <row r="279" s="12" customFormat="1">
+      <c r="A279" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B279" s="14">
+        <v>10</v>
+      </c>
+      <c r="C279" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="D279" s="16">
+        <v>0</v>
+      </c>
+      <c r="E279" s="12"/>
+      <c r="F279" s="12"/>
+    </row>
+    <row r="280" ht="35" customHeight="1">
+      <c r="A280" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B280" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="C280" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="D280" s="18" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -5517,18 +5631,18 @@
     <mergeCell ref="E4:E4"/>
     <mergeCell ref="E5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A274:D274"/>
+    <mergeCell ref="A280:D280"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
-    <hyperlink ref="B6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
-    <hyperlink ref="C6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
-    <hyperlink ref="D6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
-    <hyperlink ref="E6" location="'Historique Cours'!A274" display="Se rendre en bas du document"/>
-    <hyperlink ref="A274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="B274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="C274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="D274" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="A6" location="'Historique Cours'!A280" display="Se rendre en bas du document"/>
+    <hyperlink ref="B6" location="'Historique Cours'!A280" display="Se rendre en bas du document"/>
+    <hyperlink ref="C6" location="'Historique Cours'!A280" display="Se rendre en bas du document"/>
+    <hyperlink ref="D6" location="'Historique Cours'!A280" display="Se rendre en bas du document"/>
+    <hyperlink ref="E6" location="'Historique Cours'!A280" display="Se rendre en bas du document"/>
+    <hyperlink ref="A280" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="B280" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="C280" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="D280" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
   </hyperlinks>
   <headerFooter/>
   <tableParts>
